--- a/news_daily/2026-08-20.xlsx
+++ b/news_daily/2026-08-20.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH44"/>
+  <dimension ref="A1:BL44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -526,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1003,6 +1027,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1177,6 +1205,10 @@
       </c>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1343,6 +1375,10 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1517,6 +1553,10 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr"/>
+      <c r="BL5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1691,6 +1731,10 @@
       </c>
       <c r="BG6" s="2" t="inlineStr"/>
       <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1865,6 +1909,10 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -2031,6 +2079,10 @@
         </is>
       </c>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2205,6 +2257,10 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2379,6 +2435,10 @@
         </is>
       </c>
       <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2553,6 +2613,10 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr"/>
+      <c r="BL11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2727,6 +2791,10 @@
         </is>
       </c>
       <c r="BH12" s="3" t="inlineStr"/>
+      <c r="BI12" s="3" t="inlineStr"/>
+      <c r="BJ12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr"/>
+      <c r="BL12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -2893,6 +2961,10 @@
         </is>
       </c>
       <c r="BH13" s="3" t="inlineStr"/>
+      <c r="BI13" s="3" t="inlineStr"/>
+      <c r="BJ13" s="3" t="inlineStr"/>
+      <c r="BK13" s="3" t="inlineStr"/>
+      <c r="BL13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3067,6 +3139,10 @@
       </c>
       <c r="BG14" s="3" t="inlineStr"/>
       <c r="BH14" s="3" t="inlineStr"/>
+      <c r="BI14" s="3" t="inlineStr"/>
+      <c r="BJ14" s="3" t="inlineStr"/>
+      <c r="BK14" s="3" t="inlineStr"/>
+      <c r="BL14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3233,172 +3309,204 @@
         </is>
       </c>
       <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Warner Bros. Discovery</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>L.A. Mayor Karen Bass Throws Her Support Behind Paramount-Warner Bros. Discovery Settlement</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0.356</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUFExNlZvVjFURERKa0NDX3JHWHhrQS16VXo2N0N5azYwZ2hOOW9TRTVXTlAtOERJUXVQLUpybjJhMGg1V0dyODYxNnI0ZWUwYUc3TVpCdlVydUJseUtQYUhfSlQ0MEJDNDFEYUhxTVFwSG1rdUdqd2g1V05NSGNGSmJPVjFvNnIxcTZfYjNiaWFTMEJHckFySE9DRmJkSS1HanEyMDVEa3FJSURqUFJERWR2X1lxQVJGandmQmNidw?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>The Hollywood Reporter</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>559fcc6bde1a42f584e02e8f3d39025d</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>4cfe751a5114d2d0ebcd17e6</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t>b9e809a50f9d5ef5364a980d</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
+      <c r="AM16" s="2" t="inlineStr"/>
+      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>0.356</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUFExNlZvVjFURERKa0NDX3JHWHhrQS16VXo2N0N5azYwZ2hOOW9TRTVXTlAtOERJUXVQLUpybjJhMGg1V0dyODYxNnI0ZWUwYUc3TVpCdlVydUJseUtQYUhfSlQ0MEJDNDFEYUhxTVFwSG1rdUdqd2g1V05NSGNGSmJPVjFvNnIxcTZfYjNiaWFTMEJHckFySE9DRmJkSS1HanEyMDVEa3FJSURqUFJERWR2X1lxQVJGandmQmNidw?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>The Hollywood Reporter</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>4cfe751a5114d2d0ebcd17e6</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>b9e809a50f9d5ef5364a980d</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr"/>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
+      <c r="AP16" s="2" t="inlineStr"/>
+      <c r="AQ16" s="2" t="inlineStr"/>
+      <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr"/>
+      <c r="AT16" s="2" t="inlineStr"/>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr"/>
+      <c r="AX16" s="2" t="inlineStr"/>
+      <c r="AY16" s="2" t="inlineStr"/>
+      <c r="AZ16" s="2" t="inlineStr"/>
+      <c r="BA16" s="2" t="inlineStr"/>
+      <c r="BB16" s="2" t="inlineStr">
         <is>
           <t>WBD</t>
         </is>
       </c>
-      <c r="BC16" s="4" t="inlineStr">
+      <c r="BC16" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr">
+      <c r="BD16" s="2" t="inlineStr"/>
+      <c r="BE16" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF16" s="4" t="inlineStr"/>
-      <c r="BG16" s="4" t="inlineStr">
+      <c r="BF16" s="2" t="inlineStr"/>
+      <c r="BG16" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH16" s="4" t="inlineStr"/>
+      <c r="BH16" s="2" t="inlineStr"/>
+      <c r="BI16" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ16" s="2" t="inlineStr"/>
+      <c r="BK16" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3573,6 +3681,10 @@
         </is>
       </c>
       <c r="BH17" s="3" t="inlineStr"/>
+      <c r="BI17" s="3" t="inlineStr"/>
+      <c r="BJ17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr"/>
+      <c r="BL17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3623,13 +3735,17 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -3682,7 +3798,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="4" t="inlineStr"/>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>37f6bc60fb4e4cd280132332527d361a</t>
+        </is>
+      </c>
       <c r="AC18" s="4" t="inlineStr">
         <is>
           <t>7544ac3ce7157c7987643cd1</t>
@@ -3703,7 +3823,11 @@
       <c r="AL18" s="4" t="inlineStr"/>
       <c r="AM18" s="4" t="inlineStr"/>
       <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
+      <c r="AO18" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP18" s="4" t="inlineStr"/>
       <c r="AQ18" s="4" t="inlineStr"/>
       <c r="AR18" s="4" t="inlineStr"/>
@@ -3747,172 +3871,212 @@
         </is>
       </c>
       <c r="BH18" s="4" t="inlineStr"/>
+      <c r="BI18" s="4" t="inlineStr"/>
+      <c r="BJ18" s="4" t="inlineStr"/>
+      <c r="BK18" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Kroger</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Got prescriptions at Kroger? You may qualify for payment in $17 million proposed settlement</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZ2QxdkhxaDY5MmZsM3lldlFIVEFlNS1EZ19ZQWZpSzVGak5RdkNqenpLN0QwTlhHeVMxcnJPa2lWWU0zOGV0SERKZzdXX09YeHZjOVp0Rl83VHpGanZqU2pqamltY1FMZy1fd04tY0N1UG1nTGE1cF9lRHdNSnA2RXd3V2lsbEczS3FpNnJsei1wN29tZW9VZHpxQlpUYkNNMVBudUJxM09xbVlVU1cyRzhSeU1kSlgtVGI5c25oa29ETTl2cjFN0gHMAUFVX3lxTFAybkkwd2FpcGtwLXlKaVFPdk9aMjh4Z2JmUWxyekJ2TVFVZG1sS1R2bFRWR3dKVHlFbWxmS3pTelAxaTNlUmlIZXFwNmo2Tk5CSjN5cUNfcUY5NEhKOXE3dGtWbml0Q2FOdThOZFV6SmZtel81M0tnWVVxTE5YWHJ0Z0dJSkd2ZUtpdnFoOUJITVpDcmdQdmtmc0ZSSnJiak1KV19qVHNXV21wSkpwYnlhT052V19FLXo1Mkc5RmxfRkptcV9QcVBZV2hvcQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>fox59.com</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>058bda66e7564071a1cb593fc5c5ac28</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>5d293840c452f2f47963b605</t>
+        </is>
+      </c>
+      <c r="AD19" s="2" t="inlineStr">
+        <is>
+          <t>5a39baed1e5af1babd36a364</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
+      <c r="AL19" s="2" t="inlineStr"/>
+      <c r="AM19" s="2" t="inlineStr"/>
+      <c r="AN19" s="2" t="inlineStr"/>
+      <c r="AO19" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>0.248</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZ2QxdkhxaDY5MmZsM3lldlFIVEFlNS1EZ19ZQWZpSzVGak5RdkNqenpLN0QwTlhHeVMxcnJPa2lWWU0zOGV0SERKZzdXX09YeHZjOVp0Rl83VHpGanZqU2pqamltY1FMZy1fd04tY0N1UG1nTGE1cF9lRHdNSnA2RXd3V2lsbEczS3FpNnJsei1wN29tZW9VZHpxQlpUYkNNMVBudUJxM09xbVlVU1cyRzhSeU1kSlgtVGI5c25oa29ETTl2cjFN0gHMAUFVX3lxTFAybkkwd2FpcGtwLXlKaVFPdk9aMjh4Z2JmUWxyekJ2TVFVZG1sS1R2bFRWR3dKVHlFbWxmS3pTelAxaTNlUmlIZXFwNmo2Tk5CSjN5cUNfcUY5NEhKOXE3dGtWbml0Q2FOdThOZFV6SmZtel81M0tnWVVxTE5YWHJ0Z0dJSkd2ZUtpdnFoOUJITVpDcmdQdmtmc0ZSSnJiak1KV19qVHNXV21wSkpwYnlhT052V19FLXo1Mkc5RmxfRkptcV9QcVBZV2hvcQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>fox59.com</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>5d293840c452f2f47963b605</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>5a39baed1e5af1babd36a364</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr"/>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr"/>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
+      <c r="AP19" s="2" t="inlineStr"/>
+      <c r="AQ19" s="2" t="inlineStr"/>
+      <c r="AR19" s="2" t="inlineStr"/>
+      <c r="AS19" s="2" t="inlineStr"/>
+      <c r="AT19" s="2" t="inlineStr"/>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr"/>
+      <c r="AX19" s="2" t="inlineStr"/>
+      <c r="AY19" s="2" t="inlineStr"/>
+      <c r="AZ19" s="2" t="inlineStr"/>
+      <c r="BA19" s="2" t="inlineStr"/>
+      <c r="BB19" s="2" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="BC19" s="4" t="inlineStr">
+      <c r="BC19" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD19" s="4" t="inlineStr"/>
-      <c r="BE19" s="4" t="inlineStr">
+      <c r="BD19" s="2" t="inlineStr"/>
+      <c r="BE19" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF19" s="4" t="inlineStr"/>
-      <c r="BG19" s="4" t="inlineStr">
+      <c r="BF19" s="2" t="inlineStr"/>
+      <c r="BG19" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH19" s="4" t="inlineStr"/>
+      <c r="BH19" s="2" t="inlineStr"/>
+      <c r="BI19" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ19" s="2" t="inlineStr"/>
+      <c r="BK19" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4087,180 +4251,212 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BJ20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr"/>
+      <c r="BL20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>CME Group Inc.</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>CME CEO Spars With CFTC Chair About Prediction Market Oversight</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>'-0.03</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQl9ER0JjUC1UZ0lQUDhHTFl1dVZGUm9zZzEzd0lUVGRPcUxQSUhaU2h0ODhEd0xsX3ZoRjI3SUFqSWZlajNvdlB6QW9qckg3dnJaNHlqNU1TUTBjWndSSHVaLUlIbW1kRndjOXZ3Tnd3bkZBWlkzb3ZZdTFQbWpYWlRkbWNTdTVDZEJyVTRjMUdfbXJkNDRfRjRnZXJfNElhMDgtQTBwNGJPUkVEazVsRXhxaWs?oc=5</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg.com</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>CFTC；FTC</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>91db8ca2800d4ca3b4a37a4d05242be6</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>a6314d7a313ab5ad737cc1a5</t>
+        </is>
+      </c>
+      <c r="AD21" s="2" t="inlineStr">
+        <is>
+          <t>4ce2f2951b07ed8eb8da64ae</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+      <c r="AK21" s="2" t="inlineStr"/>
+      <c r="AL21" s="2" t="inlineStr"/>
+      <c r="AM21" s="2" t="inlineStr"/>
+      <c r="AN21" s="2" t="inlineStr"/>
+      <c r="AO21" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>'-0.03</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQl9ER0JjUC1UZ0lQUDhHTFl1dVZGUm9zZzEzd0lUVGRPcUxQSUhaU2h0ODhEd0xsX3ZoRjI3SUFqSWZlajNvdlB6QW9qckg3dnJaNHlqNU1TUTBjWndSSHVaLUlIbW1kRndjOXZ3Tnd3bkZBWlkzb3ZZdTFQbWpYWlRkbWNTdTVDZEJyVTRjMUdfbXJkNDRfRjRnZXJfNElhMDgtQTBwNGJPUkVEazVsRXhxaWs?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>Bloomberg.com</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>a6314d7a313ab5ad737cc1a5</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>4ce2f2951b07ed8eb8da64ae</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr">
+      <c r="AP21" s="2" t="inlineStr"/>
+      <c r="AQ21" s="2" t="inlineStr"/>
+      <c r="AR21" s="2" t="inlineStr"/>
+      <c r="AS21" s="2" t="inlineStr"/>
+      <c r="AT21" s="2" t="inlineStr"/>
+      <c r="AU21" s="2" t="inlineStr"/>
+      <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
+      <c r="AX21" s="2" t="inlineStr"/>
+      <c r="AY21" s="2" t="inlineStr"/>
+      <c r="AZ21" s="2" t="inlineStr"/>
+      <c r="BA21" s="2" t="inlineStr"/>
+      <c r="BB21" s="2" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
-      <c r="BC21" s="4" t="inlineStr">
+      <c r="BC21" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
+      <c r="BD21" s="2" t="inlineStr"/>
+      <c r="BE21" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF21" s="4" t="inlineStr">
+      <c r="BF21" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG21" s="4" t="inlineStr">
+      <c r="BG21" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH21" s="4" t="inlineStr"/>
+      <c r="BH21" s="2" t="inlineStr"/>
+      <c r="BI21" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ21" s="2" t="inlineStr"/>
+      <c r="BK21" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -4301,7 +4497,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -4311,13 +4507,17 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -4357,7 +4557,7 @@
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
@@ -4370,7 +4570,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB22" s="4" t="inlineStr"/>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>eac60657ffd849dab62f5ba0a3ef54a4</t>
+        </is>
+      </c>
       <c r="AC22" s="4" t="inlineStr">
         <is>
           <t>1f0369a48bb25dc74096908b</t>
@@ -4391,7 +4595,11 @@
       <c r="AL22" s="4" t="inlineStr"/>
       <c r="AM22" s="4" t="inlineStr"/>
       <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr"/>
+      <c r="AO22" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="4" t="inlineStr"/>
       <c r="AQ22" s="4" t="inlineStr"/>
       <c r="AR22" s="4" t="inlineStr"/>
@@ -4435,6 +4643,22 @@
         </is>
       </c>
       <c r="BH22" s="4" t="inlineStr"/>
+      <c r="BI22" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ22" s="4" t="inlineStr"/>
+      <c r="BK22" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -4485,13 +4709,17 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -4544,7 +4772,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB23" s="4" t="inlineStr"/>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>962629bb4d8343d8b2df0a397aafd231</t>
+        </is>
+      </c>
       <c r="AC23" s="4" t="inlineStr">
         <is>
           <t>19ac0856711e24e1eb080c0e</t>
@@ -4565,7 +4797,11 @@
       <c r="AL23" s="4" t="inlineStr"/>
       <c r="AM23" s="4" t="inlineStr"/>
       <c r="AN23" s="4" t="inlineStr"/>
-      <c r="AO23" s="4" t="inlineStr"/>
+      <c r="AO23" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP23" s="4" t="inlineStr"/>
       <c r="AQ23" s="4" t="inlineStr"/>
       <c r="AR23" s="4" t="inlineStr"/>
@@ -4601,6 +4837,18 @@
         </is>
       </c>
       <c r="BH23" s="4" t="inlineStr"/>
+      <c r="BI23" s="4" t="inlineStr"/>
+      <c r="BJ23" s="4" t="inlineStr"/>
+      <c r="BK23" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -4651,13 +4899,17 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -4710,7 +4962,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr"/>
+      <c r="AB24" s="4" t="inlineStr">
+        <is>
+          <t>77c158a40ddc4258910ac1bc386e86a2</t>
+        </is>
+      </c>
       <c r="AC24" s="4" t="inlineStr">
         <is>
           <t>5ddf20be53114d48c44012a2</t>
@@ -4731,7 +4987,11 @@
       <c r="AL24" s="4" t="inlineStr"/>
       <c r="AM24" s="4" t="inlineStr"/>
       <c r="AN24" s="4" t="inlineStr"/>
-      <c r="AO24" s="4" t="inlineStr"/>
+      <c r="AO24" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP24" s="4" t="inlineStr"/>
       <c r="AQ24" s="4" t="inlineStr"/>
       <c r="AR24" s="4" t="inlineStr"/>
@@ -4767,354 +5027,414 @@
         </is>
       </c>
       <c r="BH24" s="4" t="inlineStr"/>
+      <c r="BI24" s="4" t="inlineStr"/>
+      <c r="BJ24" s="4" t="inlineStr"/>
+      <c r="BK24" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>CME Group Inc.</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>CFTC Innovation Advisory Committee meeting: CME Group CEO Warns About Prediction Market Listings Open to Manipulation</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr"/>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>'-0.894</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOR1FjYm1fS2xld2hJZFlZVGJMaFd4OXJUajJsX0xYZEwtcDZEZS1EUkNjdi1qZUtQQTNyRVozUVR3TkNYbHU4RV9GRTdtbTFPMEZlQV9HbUdSb01MVmRwdVJBRUI2VkVQZm9GMlRSalJsZWF0cXppUzJnY2pfNlpmcVdsYnZHWVhnOFBhekdFZGVoOU56b1QwZ3JZeGd5UF9xcjFRZldKN1lQWWFHdlFKX2FXSlUzLVV5OXJrOXRpT1VvS2tuSUR1VThiSm1qdVBzSHE5VXIzR1huakpDWGpnZlcyS1VEejBBR0tUUXBWek9aMzNmY3MxVg?oc=5</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Crowdfund Insider</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>CFTC；FTC</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>b562274948b347d09c98fcf7e5be9e1e</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>8c37fce9611dc02868f91729</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>29ca53ec6f51746b22cb1b98</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+      <c r="AK25" s="2" t="inlineStr"/>
+      <c r="AL25" s="2" t="inlineStr"/>
+      <c r="AM25" s="2" t="inlineStr"/>
+      <c r="AN25" s="2" t="inlineStr"/>
+      <c r="AO25" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr">
-        <is>
-          <t>'-0.894</t>
-        </is>
-      </c>
-      <c r="P25" s="4" t="inlineStr"/>
-      <c r="Q25" s="4" t="inlineStr"/>
-      <c r="R25" s="4" t="inlineStr"/>
-      <c r="S25" s="4" t="inlineStr"/>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOR1FjYm1fS2xld2hJZFlZVGJMaFd4OXJUajJsX0xYZEwtcDZEZS1EUkNjdi1qZUtQQTNyRVozUVR3TkNYbHU4RV9GRTdtbTFPMEZlQV9HbUdSb01MVmRwdVJBRUI2VkVQZm9GMlRSalJsZWF0cXppUzJnY2pfNlpmcVdsYnZHWVhnOFBhekdFZGVoOU56b1QwZ3JZeGd5UF9xcjFRZldKN1lQWWFHdlFKX2FXSlUzLVV5OXJrOXRpT1VvS2tuSUR1VThiSm1qdVBzSHE5VXIzR1huakpDWGpnZlcyS1VEejBBR0tUUXBWek9aMzNmY3MxVg?oc=5</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>Crowdfund Insider</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr"/>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z25" s="4" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA25" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="4" t="inlineStr"/>
-      <c r="AC25" s="4" t="inlineStr">
-        <is>
-          <t>8c37fce9611dc02868f91729</t>
-        </is>
-      </c>
-      <c r="AD25" s="4" t="inlineStr">
-        <is>
-          <t>29ca53ec6f51746b22cb1b98</t>
-        </is>
-      </c>
-      <c r="AE25" s="4" t="inlineStr"/>
-      <c r="AF25" s="4" t="inlineStr"/>
-      <c r="AG25" s="4" t="inlineStr"/>
-      <c r="AH25" s="4" t="inlineStr"/>
-      <c r="AI25" s="4" t="inlineStr"/>
-      <c r="AJ25" s="4" t="inlineStr"/>
-      <c r="AK25" s="4" t="inlineStr"/>
-      <c r="AL25" s="4" t="inlineStr"/>
-      <c r="AM25" s="4" t="inlineStr"/>
-      <c r="AN25" s="4" t="inlineStr"/>
-      <c r="AO25" s="4" t="inlineStr"/>
-      <c r="AP25" s="4" t="inlineStr"/>
-      <c r="AQ25" s="4" t="inlineStr"/>
-      <c r="AR25" s="4" t="inlineStr"/>
-      <c r="AS25" s="4" t="inlineStr"/>
-      <c r="AT25" s="4" t="inlineStr"/>
-      <c r="AU25" s="4" t="inlineStr"/>
-      <c r="AV25" s="4" t="inlineStr"/>
-      <c r="AW25" s="4" t="inlineStr">
+      <c r="AP25" s="2" t="inlineStr"/>
+      <c r="AQ25" s="2" t="inlineStr"/>
+      <c r="AR25" s="2" t="inlineStr"/>
+      <c r="AS25" s="2" t="inlineStr"/>
+      <c r="AT25" s="2" t="inlineStr"/>
+      <c r="AU25" s="2" t="inlineStr"/>
+      <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" s="2" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX25" s="4" t="inlineStr"/>
-      <c r="AY25" s="4" t="inlineStr"/>
-      <c r="AZ25" s="4" t="inlineStr"/>
-      <c r="BA25" s="4" t="inlineStr"/>
-      <c r="BB25" s="4" t="inlineStr">
+      <c r="AX25" s="2" t="inlineStr"/>
+      <c r="AY25" s="2" t="inlineStr"/>
+      <c r="AZ25" s="2" t="inlineStr"/>
+      <c r="BA25" s="2" t="inlineStr"/>
+      <c r="BB25" s="2" t="inlineStr">
         <is>
           <t>CME</t>
         </is>
       </c>
-      <c r="BC25" s="4" t="inlineStr">
+      <c r="BC25" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD25" s="4" t="inlineStr"/>
-      <c r="BE25" s="4" t="inlineStr">
+      <c r="BD25" s="2" t="inlineStr"/>
+      <c r="BE25" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF25" s="4" t="inlineStr">
+      <c r="BF25" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG25" s="4" t="inlineStr">
+      <c r="BG25" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH25" s="4" t="inlineStr"/>
+      <c r="BH25" s="2" t="inlineStr"/>
+      <c r="BI25" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ25" s="2" t="inlineStr"/>
+      <c r="BK25" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Dominion Energy</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Declaring ‘economic D-Day,’ Trump says any country trading with Iran will be sanctioned</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K26" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.064</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUW9hZVlPQXhRVER0YkNDM01PVUpFYUtEWFBSUFVQcWE5TDgxOTNPSnVzeThVYldZWVZqYUhSZVRZb0hvT200ZjZ3WW9UUmV4OVc0Q21mQ0ZkMXBmZlZWNjhKaE53akF2YjFxaW5MM3d1SVJ1TVBwRXBaanhsQk1BdDRMZW00YVdHSEpYSjA2OUJLaWVDdV94aGJCOGRRVndTc1pCTFNKWnRnSlJfdWRBREhrRzJIQdIBuwFBVV95cUxNVlYwaUJHaWRocnlZbUllTDdlS1pGZmhYd3RyUTN2STZmeXpTLWZLalRsbjJNYldQNFp4eUpWd3dmWHBNTXMxZTFjOWtlR01HOFRSX1RJSmNad2p1dGw2ZWgxb0ZHbFJ0QjR2aEVDWS0ycE05QnRTLUhnbzFtWUJNeHo1ZVV5alZUaHVzdFFDYm9xZjh3cWtiR3Y1RHJXZ0FHN1VRNU13SG5XUzAzNmxZT1Zlc0RKTGEyaHA0?oc=5</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>The Times of Israel</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>sanctioned</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>a132aeae73124fc29809628587eb3a8a</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>85cb731df7d7894e88040b4d</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>65dd2640523a4c6c2f9ce79a</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr"/>
+      <c r="AL26" s="2" t="inlineStr"/>
+      <c r="AM26" s="2" t="inlineStr"/>
+      <c r="AN26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>0.064</t>
-        </is>
-      </c>
-      <c r="P26" s="4" t="inlineStr"/>
-      <c r="Q26" s="4" t="inlineStr"/>
-      <c r="R26" s="4" t="inlineStr"/>
-      <c r="S26" s="4" t="inlineStr"/>
-      <c r="T26" s="4" t="inlineStr">
+      <c r="AP26" s="2" t="inlineStr"/>
+      <c r="AQ26" s="2" t="inlineStr"/>
+      <c r="AR26" s="2" t="inlineStr"/>
+      <c r="AS26" s="2" t="inlineStr"/>
+      <c r="AT26" s="2" t="inlineStr"/>
+      <c r="AU26" s="2" t="inlineStr"/>
+      <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" s="2" t="inlineStr"/>
+      <c r="AX26" s="2" t="inlineStr"/>
+      <c r="AY26" s="2" t="inlineStr"/>
+      <c r="AZ26" s="2" t="inlineStr"/>
+      <c r="BA26" s="2" t="inlineStr"/>
+      <c r="BB26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BC26" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUW9hZVlPQXhRVER0YkNDM01PVUpFYUtEWFBSUFVQcWE5TDgxOTNPSnVzeThVYldZWVZqYUhSZVRZb0hvT200ZjZ3WW9UUmV4OVc0Q21mQ0ZkMXBmZlZWNjhKaE53akF2YjFxaW5MM3d1SVJ1TVBwRXBaanhsQk1BdDRMZW00YVdHSEpYSjA2OUJLaWVDdV94aGJCOGRRVndTc1pCTFNKWnRnSlJfdWRBREhrRzJIQdIBuwFBVV95cUxNVlYwaUJHaWRocnlZbUllTDdlS1pGZmhYd3RyUTN2STZmeXpTLWZLalRsbjJNYldQNFp4eUpWd3dmWHBNTXMxZTFjOWtlR01HOFRSX1RJSmNad2p1dGw2ZWgxb0ZHbFJ0QjR2aEVDWS0ycE05QnRTLUhnbzFtWUJNeHo1ZVV5alZUaHVzdFFDYm9xZjh3cWtiR3Y1RHJXZ0FHN1VRNU13SG5XUzAzNmxZT1Zlc0RKTGEyaHA0?oc=5</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>The Times of Israel</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="inlineStr"/>
-      <c r="X26" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z26" s="4" t="inlineStr">
-        <is>
-          <t>sanctioned</t>
-        </is>
-      </c>
-      <c r="AA26" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="4" t="inlineStr"/>
-      <c r="AC26" s="4" t="inlineStr">
-        <is>
-          <t>85cb731df7d7894e88040b4d</t>
-        </is>
-      </c>
-      <c r="AD26" s="4" t="inlineStr">
-        <is>
-          <t>65dd2640523a4c6c2f9ce79a</t>
-        </is>
-      </c>
-      <c r="AE26" s="4" t="inlineStr"/>
-      <c r="AF26" s="4" t="inlineStr"/>
-      <c r="AG26" s="4" t="inlineStr"/>
-      <c r="AH26" s="4" t="inlineStr"/>
-      <c r="AI26" s="4" t="inlineStr"/>
-      <c r="AJ26" s="4" t="inlineStr"/>
-      <c r="AK26" s="4" t="inlineStr"/>
-      <c r="AL26" s="4" t="inlineStr"/>
-      <c r="AM26" s="4" t="inlineStr"/>
-      <c r="AN26" s="4" t="inlineStr"/>
-      <c r="AO26" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP26" s="4" t="inlineStr"/>
-      <c r="AQ26" s="4" t="inlineStr"/>
-      <c r="AR26" s="4" t="inlineStr"/>
-      <c r="AS26" s="4" t="inlineStr"/>
-      <c r="AT26" s="4" t="inlineStr"/>
-      <c r="AU26" s="4" t="inlineStr"/>
-      <c r="AV26" s="4" t="inlineStr"/>
-      <c r="AW26" s="4" t="inlineStr"/>
-      <c r="AX26" s="4" t="inlineStr"/>
-      <c r="AY26" s="4" t="inlineStr"/>
-      <c r="AZ26" s="4" t="inlineStr"/>
-      <c r="BA26" s="4" t="inlineStr"/>
-      <c r="BB26" s="4" t="inlineStr">
+      <c r="BD26" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="BC26" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD26" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="BE26" s="4" t="inlineStr">
+      <c r="BE26" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF26" s="4" t="inlineStr">
+      <c r="BF26" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG26" s="4" t="inlineStr"/>
-      <c r="BH26" s="4" t="inlineStr"/>
+      <c r="BG26" s="2" t="inlineStr"/>
+      <c r="BH26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5289,6 +5609,10 @@
         </is>
       </c>
       <c r="BH27" s="3" t="inlineStr"/>
+      <c r="BI27" s="3" t="inlineStr"/>
+      <c r="BJ27" s="3" t="inlineStr"/>
+      <c r="BK27" s="3" t="inlineStr"/>
+      <c r="BL27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5455,6 +5779,10 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BJ28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr"/>
+      <c r="BL28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5629,6 +5957,10 @@
         </is>
       </c>
       <c r="BH29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BJ29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr"/>
+      <c r="BL29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5795,6 +6127,10 @@
       <c r="BF30" s="2" t="inlineStr"/>
       <c r="BG30" s="2" t="inlineStr"/>
       <c r="BH30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BJ30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr"/>
+      <c r="BL30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -5961,6 +6297,10 @@
       <c r="BF31" s="2" t="inlineStr"/>
       <c r="BG31" s="2" t="inlineStr"/>
       <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr"/>
+      <c r="BL31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6135,6 +6475,10 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BJ32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr"/>
+      <c r="BL32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6309,6 +6653,10 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BJ33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr"/>
+      <c r="BL33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6483,6 +6831,10 @@
       </c>
       <c r="BG34" s="2" t="inlineStr"/>
       <c r="BH34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BJ34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr"/>
+      <c r="BL34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6657,6 +7009,10 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BJ35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr"/>
+      <c r="BL35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6815,6 +7171,10 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI36" s="2" t="inlineStr"/>
+      <c r="BJ36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr"/>
+      <c r="BL36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -6973,6 +7333,10 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
+      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BJ37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr"/>
+      <c r="BL37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7147,6 +7511,10 @@
         </is>
       </c>
       <c r="BH38" s="2" t="inlineStr"/>
+      <c r="BI38" s="2" t="inlineStr"/>
+      <c r="BJ38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr"/>
+      <c r="BL38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7321,6 +7689,10 @@
         </is>
       </c>
       <c r="BH39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr"/>
+      <c r="BJ39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr"/>
+      <c r="BL39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7487,6 +7859,10 @@
         </is>
       </c>
       <c r="BH40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr"/>
+      <c r="BJ40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr"/>
+      <c r="BL40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7653,350 +8029,402 @@
       <c r="BF41" s="2" t="inlineStr"/>
       <c r="BG41" s="2" t="inlineStr"/>
       <c r="BH41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BJ41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr"/>
+      <c r="BL41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Intercontinental Exchange Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T06:07:05+08:00</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Colorado attorney general sues ​ICE detention center operator ​i​n tuberculosis ​case</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>'-0.923</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9mTl81MjBxWW1ncEJ6S2hWNUFLdzdZaDduOElPc1FhTmJ0VHlQUHViOVNQWThCWC1JemU1QkVmbE05d2s4V3N5Rm9NWGwxRFdoUzAtS2JhQkdLNWZ6bkJDS19PdWtQaF9aanM5M1R1dWJkeTdTeFRXZk1QOA?oc=5</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Colorado Newsline</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>attorney general</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>312d5829584e4f608baeaf3827886ee6</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>72cca324c95efb8846f49b57</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>432e70cfc3cd017e4c677aa0</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+      <c r="AK42" s="2" t="inlineStr"/>
+      <c r="AL42" s="2" t="inlineStr"/>
+      <c r="AM42" s="2" t="inlineStr"/>
+      <c r="AN42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr"/>
-      <c r="Q42" s="4" t="inlineStr"/>
-      <c r="R42" s="4" t="inlineStr"/>
-      <c r="S42" s="4" t="inlineStr"/>
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U42" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9mTl81MjBxWW1ncEJ6S2hWNUFLdzdZaDduOElPc1FhTmJ0VHlQUHViOVNQWThCWC1JemU1QkVmbE05d2s4V3N5Rm9NWGwxRFdoUzAtS2JhQkdLNWZ6bkJDS19PdWtQaF9aanM5M1R1dWJkeTdTeFRXZk1QOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V42" s="4" t="inlineStr">
-        <is>
-          <t>Colorado Newsline</t>
-        </is>
-      </c>
-      <c r="W42" s="4" t="inlineStr"/>
-      <c r="X42" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y42" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z42" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA42" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="4" t="inlineStr"/>
-      <c r="AC42" s="4" t="inlineStr">
-        <is>
-          <t>72cca324c95efb8846f49b57</t>
-        </is>
-      </c>
-      <c r="AD42" s="4" t="inlineStr">
-        <is>
-          <t>432e70cfc3cd017e4c677aa0</t>
-        </is>
-      </c>
-      <c r="AE42" s="4" t="inlineStr"/>
-      <c r="AF42" s="4" t="inlineStr"/>
-      <c r="AG42" s="4" t="inlineStr"/>
-      <c r="AH42" s="4" t="inlineStr"/>
-      <c r="AI42" s="4" t="inlineStr"/>
-      <c r="AJ42" s="4" t="inlineStr"/>
-      <c r="AK42" s="4" t="inlineStr"/>
-      <c r="AL42" s="4" t="inlineStr"/>
-      <c r="AM42" s="4" t="inlineStr"/>
-      <c r="AN42" s="4" t="inlineStr"/>
-      <c r="AO42" s="4" t="inlineStr"/>
-      <c r="AP42" s="4" t="inlineStr"/>
-      <c r="AQ42" s="4" t="inlineStr"/>
-      <c r="AR42" s="4" t="inlineStr"/>
-      <c r="AS42" s="4" t="inlineStr"/>
-      <c r="AT42" s="4" t="inlineStr"/>
-      <c r="AU42" s="4" t="inlineStr"/>
-      <c r="AV42" s="4" t="inlineStr"/>
-      <c r="AW42" s="4" t="inlineStr">
+      <c r="AP42" s="2" t="inlineStr"/>
+      <c r="AQ42" s="2" t="inlineStr"/>
+      <c r="AR42" s="2" t="inlineStr"/>
+      <c r="AS42" s="2" t="inlineStr"/>
+      <c r="AT42" s="2" t="inlineStr"/>
+      <c r="AU42" s="2" t="inlineStr"/>
+      <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX42" s="4" t="inlineStr"/>
-      <c r="AY42" s="4" t="inlineStr"/>
-      <c r="AZ42" s="4" t="inlineStr"/>
-      <c r="BA42" s="4" t="inlineStr"/>
-      <c r="BB42" s="4" t="inlineStr">
+      <c r="AX42" s="2" t="inlineStr"/>
+      <c r="AY42" s="2" t="inlineStr"/>
+      <c r="AZ42" s="2" t="inlineStr"/>
+      <c r="BA42" s="2" t="inlineStr"/>
+      <c r="BB42" s="2" t="inlineStr">
         <is>
           <t>ICE</t>
         </is>
       </c>
-      <c r="BC42" s="4" t="inlineStr">
+      <c r="BC42" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD42" s="4" t="inlineStr"/>
-      <c r="BE42" s="4" t="inlineStr">
+      <c r="BD42" s="2" t="inlineStr"/>
+      <c r="BE42" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF42" s="4" t="inlineStr">
+      <c r="BF42" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG42" s="4" t="inlineStr">
+      <c r="BG42" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH42" s="4" t="inlineStr"/>
+      <c r="BH42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ42" s="2" t="inlineStr"/>
+      <c r="BK42" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr"/>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Delta Air Lines</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T05:13:58+08:00</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>美國聯邦貿易委員會（FTC）正考慮要求披露個性化定價</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NYSE-DAL/news/</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>FTC</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>8917976fa73d46fb8c0a4add5c0ca04f</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>5a8dc1a140bbb656bc23cba9</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>22a56251dfb3f01a27778045</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+      <c r="AK43" s="2" t="inlineStr"/>
+      <c r="AL43" s="2" t="inlineStr"/>
+      <c r="AM43" s="2" t="inlineStr"/>
+      <c r="AN43" s="2" t="inlineStr"/>
+      <c r="AO43" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr"/>
-      <c r="P43" s="4" t="inlineStr"/>
-      <c r="Q43" s="4" t="inlineStr"/>
-      <c r="R43" s="4" t="inlineStr"/>
-      <c r="S43" s="4" t="inlineStr"/>
-      <c r="T43" s="4" t="inlineStr">
+      <c r="AP43" s="2" t="inlineStr"/>
+      <c r="AQ43" s="2" t="inlineStr"/>
+      <c r="AR43" s="2" t="inlineStr"/>
+      <c r="AS43" s="2" t="inlineStr"/>
+      <c r="AT43" s="2" t="inlineStr"/>
+      <c r="AU43" s="2" t="inlineStr"/>
+      <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" s="2" t="inlineStr"/>
+      <c r="AX43" s="2" t="inlineStr"/>
+      <c r="AY43" s="2" t="inlineStr"/>
+      <c r="AZ43" s="2" t="inlineStr"/>
+      <c r="BA43" s="2" t="inlineStr"/>
+      <c r="BB43" s="2" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="BC43" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U43" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DAL/news/</t>
-        </is>
-      </c>
-      <c r="V43" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W43" s="4" t="inlineStr"/>
-      <c r="X43" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y43" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z43" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA43" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="4" t="inlineStr"/>
-      <c r="AC43" s="4" t="inlineStr">
-        <is>
-          <t>5a8dc1a140bbb656bc23cba9</t>
-        </is>
-      </c>
-      <c r="AD43" s="4" t="inlineStr">
-        <is>
-          <t>22a56251dfb3f01a27778045</t>
-        </is>
-      </c>
-      <c r="AE43" s="4" t="inlineStr"/>
-      <c r="AF43" s="4" t="inlineStr"/>
-      <c r="AG43" s="4" t="inlineStr"/>
-      <c r="AH43" s="4" t="inlineStr"/>
-      <c r="AI43" s="4" t="inlineStr"/>
-      <c r="AJ43" s="4" t="inlineStr"/>
-      <c r="AK43" s="4" t="inlineStr"/>
-      <c r="AL43" s="4" t="inlineStr"/>
-      <c r="AM43" s="4" t="inlineStr"/>
-      <c r="AN43" s="4" t="inlineStr"/>
-      <c r="AO43" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP43" s="4" t="inlineStr"/>
-      <c r="AQ43" s="4" t="inlineStr"/>
-      <c r="AR43" s="4" t="inlineStr"/>
-      <c r="AS43" s="4" t="inlineStr"/>
-      <c r="AT43" s="4" t="inlineStr"/>
-      <c r="AU43" s="4" t="inlineStr"/>
-      <c r="AV43" s="4" t="inlineStr"/>
-      <c r="AW43" s="4" t="inlineStr"/>
-      <c r="AX43" s="4" t="inlineStr"/>
-      <c r="AY43" s="4" t="inlineStr"/>
-      <c r="AZ43" s="4" t="inlineStr"/>
-      <c r="BA43" s="4" t="inlineStr"/>
-      <c r="BB43" s="4" t="inlineStr">
+      <c r="BD43" s="2" t="inlineStr">
         <is>
           <t>DAL</t>
         </is>
       </c>
-      <c r="BC43" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD43" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="BE43" s="4" t="inlineStr">
+      <c r="BE43" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF43" s="4" t="inlineStr">
+      <c r="BF43" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG43" s="4" t="inlineStr"/>
-      <c r="BH43" s="4" t="inlineStr"/>
+      <c r="BG43" s="2" t="inlineStr"/>
+      <c r="BH43" s="2" t="inlineStr"/>
+      <c r="BI43" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ43" s="2" t="inlineStr"/>
+      <c r="BK43" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -8171,9 +8599,13 @@
         </is>
       </c>
       <c r="BH44" s="3" t="inlineStr"/>
+      <c r="BI44" s="3" t="inlineStr"/>
+      <c r="BJ44" s="3" t="inlineStr"/>
+      <c r="BK44" s="3" t="inlineStr"/>
+      <c r="BL44" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH44"/>
+  <autoFilter ref="A1:BL44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8184,7 +8616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BL16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8247,6 +8679,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8548,6 +8984,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -8716,6 +9172,10 @@
         </is>
       </c>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr"/>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr"/>
+      <c r="BL2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -8890,6 +9350,10 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr"/>
+      <c r="BL3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -9064,6 +9528,10 @@
         </is>
       </c>
       <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr"/>
+      <c r="BL4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -9238,6 +9706,10 @@
         </is>
       </c>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -9412,6 +9884,10 @@
         </is>
       </c>
       <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr"/>
+      <c r="BL6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -9578,6 +10054,10 @@
         </is>
       </c>
       <c r="BH7" s="3" t="inlineStr"/>
+      <c r="BI7" s="3" t="inlineStr"/>
+      <c r="BJ7" s="3" t="inlineStr"/>
+      <c r="BK7" s="3" t="inlineStr"/>
+      <c r="BL7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -9752,6 +10232,10 @@
       </c>
       <c r="BG8" s="3" t="inlineStr"/>
       <c r="BH8" s="3" t="inlineStr"/>
+      <c r="BI8" s="3" t="inlineStr"/>
+      <c r="BJ8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr"/>
+      <c r="BL8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -9918,346 +10402,386 @@
         </is>
       </c>
       <c r="BH9" s="3" t="inlineStr"/>
+      <c r="BI9" s="3" t="inlineStr"/>
+      <c r="BJ9" s="3" t="inlineStr"/>
+      <c r="BK9" s="3" t="inlineStr"/>
+      <c r="BL9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Starbucks Corporation</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>L.A. Mayor Karen Bass Throws Her Support Behind Paramount-Warner Bros. Discovery Settlement</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Starbucks layoffs hit 224 Seattle headquarters employees</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="N10" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>0.356</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.959</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxOUFExNlZvVjFURERKa0NDX3JHWHhrQS16VXo2N0N5azYwZ2hOOW9TRTVXTlAtOERJUXVQLUpybjJhMGg1V0dyODYxNnI0ZWUwYUc3TVpCdlVydUJseUtQYUhfSlQ0MEJDNDFEYUhxTVFwSG1rdUdqd2g1V05NSGNGSmJPVjFvNnIxcTZfYjNiaWFTMEJHckFySE9DRmJkSS1HanEyMDVEa3FJSURqUFJERWR2X1lxQVJGandmQmNidw?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>The Hollywood Reporter</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNLXBaMkcyQTUzUnFPa0I4OWduRXRBUnFNTml3TXhfV3BpbVh5Y082bVRFdkFSWG01aF9aWVJGWXRHMFBrNl9Hdk96eDFzYkxqRTVSVEdPQWY4SHVEcGY4TTNTWHA0NWxtdUlHeDRfY25oR0JVX3FvMDVGQnl1LUpEQUNKajRFUktOWGp3WE1XLVhEbmpfOUlsS2FENUd3d0pocldhZ05mOEZUcjJfUVHSAbMBQVVfeXFMTjlxSHpUbFdwd2ZhWXVQMGFTZ0xQMjNoQWVJeTgzWXE5aVh6cFFTTzY0eDB1eDRaRW9YZmtfb2lKRGVqZl90TTg0ak93MEI3ZGhPRzFGa09Bbk9xTnlScURocmJ5TnVxNFN0c0VzelNDaFdtZzZSYzVxcy01eW9pTlF0VDdDLUdCWDl0S0hiMThZQ2JkT09fMDloUHN0bnpzTGJWM0F6RVRtdkdDYzd2eVNNeFU?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>FOX 13 Seattle</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>4cfe751a5114d2d0ebcd17e6</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>b9e809a50f9d5ef5364a980d</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr"/>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>321791372228eac0ca214be6</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>14578c2488499cd965a7a8aa</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="inlineStr"/>
-      <c r="BG10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG10" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks Corporation</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks layoffs hit 224 Seattle headquarters employees</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Carson reaches $370-million settlement with Marathon Petroleum, resolving tax dispute</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>0.745</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr"/>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr"/>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcTNPaGlmWDVNendkZnp4UjZPTzdMQ2hONWh5SG5Dek9ZSXJqRzZaTjctLVYxRDd4QWdfZTM5LWZFT1F6N3pHU0lnN0tqeUF0TzBlNDA3ZlpEWGNiaDFqYlRBMEllOXE3RGZZU0pubkE2eHJGaldBNWtnT1JCenNQUk1kMWtUZm1vTlJvaGs1NkVaVmtERnM2MkdR?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr"/>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>37f6bc60fb4e4cd280132332527d361a</t>
+        </is>
+      </c>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>7544ac3ce7157c7987643cd1</t>
+        </is>
+      </c>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>261167cb765c78558992776c</t>
+        </is>
+      </c>
+      <c r="AE11" s="4" t="inlineStr"/>
+      <c r="AF11" s="4" t="inlineStr"/>
+      <c r="AG11" s="4" t="inlineStr"/>
+      <c r="AH11" s="4" t="inlineStr"/>
+      <c r="AI11" s="4" t="inlineStr"/>
+      <c r="AJ11" s="4" t="inlineStr"/>
+      <c r="AK11" s="4" t="inlineStr"/>
+      <c r="AL11" s="4" t="inlineStr"/>
+      <c r="AM11" s="4" t="inlineStr"/>
+      <c r="AN11" s="4" t="inlineStr"/>
+      <c r="AO11" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>'-0.959</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr"/>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNLXBaMkcyQTUzUnFPa0I4OWduRXRBUnFNTml3TXhfV3BpbVh5Y082bVRFdkFSWG01aF9aWVJGWXRHMFBrNl9Hdk96eDFzYkxqRTVSVEdPQWY4SHVEcGY4TTNTWHA0NWxtdUlHeDRfY25oR0JVX3FvMDVGQnl1LUpEQUNKajRFUktOWGp3WE1XLVhEbmpfOUlsS2FENUd3d0pocldhZ05mOEZUcjJfUVHSAbMBQVVfeXFMTjlxSHpUbFdwd2ZhWXVQMGFTZ0xQMjNoQWVJeTgzWXE5aVh6cFFTTzY0eDB1eDRaRW9YZmtfb2lKRGVqZl90TTg0ak93MEI3ZGhPRzFGa09Bbk9xTnlScURocmJ5TnVxNFN0c0VzelNDaFdtZzZSYzVxcy01eW9pTlF0VDdDLUdCWDl0S0hiMThZQ2JkT09fMDloUHN0bnpzTGJWM0F6RVRtdkdDYzd2eVNNeFU?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>FOX 13 Seattle</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>321791372228eac0ca214be6</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>14578c2488499cd965a7a8aa</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="inlineStr"/>
-      <c r="AF11" s="3" t="inlineStr"/>
-      <c r="AG11" s="3" t="inlineStr"/>
-      <c r="AH11" s="3" t="inlineStr"/>
-      <c r="AI11" s="3" t="inlineStr"/>
-      <c r="AJ11" s="3" t="inlineStr"/>
-      <c r="AK11" s="3" t="inlineStr"/>
-      <c r="AL11" s="3" t="inlineStr"/>
-      <c r="AM11" s="3" t="inlineStr"/>
-      <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
-      <c r="AR11" s="3" t="inlineStr"/>
-      <c r="AS11" s="3" t="inlineStr"/>
-      <c r="AT11" s="3" t="inlineStr"/>
-      <c r="AU11" s="3" t="inlineStr"/>
-      <c r="AV11" s="3" t="inlineStr"/>
-      <c r="AW11" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX11" s="3" t="inlineStr"/>
-      <c r="AY11" s="3" t="inlineStr"/>
-      <c r="AZ11" s="3" t="inlineStr"/>
-      <c r="BA11" s="3" t="inlineStr"/>
-      <c r="BB11" s="3" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="BC11" s="3" t="inlineStr">
+      <c r="AP11" s="4" t="inlineStr"/>
+      <c r="AQ11" s="4" t="inlineStr"/>
+      <c r="AR11" s="4" t="inlineStr"/>
+      <c r="AS11" s="4" t="inlineStr"/>
+      <c r="AT11" s="4" t="inlineStr"/>
+      <c r="AU11" s="4" t="inlineStr"/>
+      <c r="AV11" s="4" t="inlineStr"/>
+      <c r="AW11" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX11" s="4" t="inlineStr"/>
+      <c r="AY11" s="4" t="inlineStr"/>
+      <c r="AZ11" s="4" t="inlineStr"/>
+      <c r="BA11" s="4" t="inlineStr"/>
+      <c r="BB11" s="4" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="BC11" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="3" t="inlineStr"/>
-      <c r="BE11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="3" t="inlineStr">
+      <c r="BD11" s="4" t="inlineStr"/>
+      <c r="BE11" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG11" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI11" s="4" t="inlineStr"/>
+      <c r="BJ11" s="4" t="inlineStr"/>
+      <c r="BK11" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -10272,12 +10796,12 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Marathon Petroleum Corporation Common Stock</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -10287,7 +10811,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Carson reaches $370-million settlement with Marathon Petroleum, resolving tax dispute</t>
+          <t>Abbott in $670M settlement for some NEC infant formula claims (ABT:NYSE)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
@@ -10298,7 +10822,7 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -10308,13 +10832,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -10324,7 +10852,7 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>'-0.492</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr"/>
@@ -10338,12 +10866,12 @@
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcTNPaGlmWDVNendkZnp4UjZPTzdMQ2hONWh5SG5Dek9ZSXJqRzZaTjctLVYxRDd4QWdfZTM5LWZFT1F6N3pHU0lnN0tqeUF0TzBlNDA3ZlpEWGNiaDFqYlRBMEllOXE3RGZZU0pubkE2eHJGaldBNWtnT1JCenNQUk1kMWtUZm1vTlJvaGs1NkVaVmtERnM2MkdR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNcWMxOVUxR0pMYkkwVmlQaGd3eUR0NnZkT2RoWnF2RzNVS1dVSlNHVVlQd1hfa05nN2p4MUFjRGdET2x2MTlvdW51cFpXVW1sWTRfNkRIZ0hVTjFtOHJuTnE2LVBBdWNHYWlLeXQ4b1dzUmlOWnRVcGRhOXV5cWkxbjdOcW00UVExWmVZQlA0dXc5NFpCU1E?oc=5</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>Seeking Alpha</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr"/>
@@ -10354,7 +10882,7 @@
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
@@ -10367,15 +10895,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>eac60657ffd849dab62f5ba0a3ef54a4</t>
+        </is>
+      </c>
       <c r="AC12" s="4" t="inlineStr">
         <is>
-          <t>7544ac3ce7157c7987643cd1</t>
+          <t>1f0369a48bb25dc74096908b</t>
         </is>
       </c>
       <c r="AD12" s="4" t="inlineStr">
         <is>
-          <t>261167cb765c78558992776c</t>
+          <t>202eba2fa538a72147f07e7f</t>
         </is>
       </c>
       <c r="AE12" s="4" t="inlineStr"/>
@@ -10388,7 +10920,11 @@
       <c r="AL12" s="4" t="inlineStr"/>
       <c r="AM12" s="4" t="inlineStr"/>
       <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="4" t="inlineStr"/>
       <c r="AQ12" s="4" t="inlineStr"/>
       <c r="AR12" s="4" t="inlineStr"/>
@@ -10407,7 +10943,7 @@
       <c r="BA12" s="4" t="inlineStr"/>
       <c r="BB12" s="4" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="BC12" s="4" t="inlineStr">
@@ -10418,20 +10954,36 @@
       <c r="BD12" s="4" t="inlineStr"/>
       <c r="BE12" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
         </is>
       </c>
       <c r="BF12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="BG12" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>上市公司</t>
         </is>
       </c>
       <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -10446,12 +10998,12 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Kroger</t>
+          <t>Warner Bros. Discovery</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -10461,7 +11013,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Got prescriptions at Kroger? You may qualify for payment in $17 million proposed settlement</t>
+          <t>California Attorney General Rob Bonta: Paramount-WBD lawsuit is a 'black-and-white' antitrust case</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
@@ -10472,7 +11024,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -10482,13 +11034,17 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -10498,7 +11054,7 @@
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>'-0.552</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -10512,12 +11068,12 @@
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxQZ2QxdkhxaDY5MmZsM3lldlFIVEFlNS1EZ19ZQWZpSzVGak5RdkNqenpLN0QwTlhHeVMxcnJPa2lWWU0zOGV0SERKZzdXX09YeHZjOVp0Rl83VHpGanZqU2pqamltY1FMZy1fd04tY0N1UG1nTGE1cF9lRHdNSnA2RXd3V2lsbEczS3FpNnJsei1wN29tZW9VZHpxQlpUYkNNMVBudUJxM09xbVlVU1cyRzhSeU1kSlgtVGI5c25oa29ETTl2cjFN0gHMAUFVX3lxTFAybkkwd2FpcGtwLXlKaVFPdk9aMjh4Z2JmUWxyekJ2TVFVZG1sS1R2bFRWR3dKVHlFbWxmS3pTelAxaTNlUmlIZXFwNmo2Tk5CSjN5cUNfcUY5NEhKOXE3dGtWbml0Q2FOdThOZFV6SmZtel81M0tnWVVxTE5YWHJ0Z0dJSkd2ZUtpdnFoOUJITVpDcmdQdmtmc0ZSSnJiak1KV19qVHNXV21wSkpwYnlhT052V19FLXo1Mkc5RmxfRkptcV9QcVBZV2hvcQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVGFJMndFT0FkV2Zfb1I3Qy1hQWFGV2tWVzJONzM2ODFLR0l3bjVhX3dCWVo4dnlMaERVYWhDVTB4dTlUNG1TMHJFSjZEcUgyR3kxSFhIb0tnWDVFRDVjeEcyTDBnV0ZWME5BMmxPbHl6NlR2Y2p0R1hkWDVtcDJ5dmJBcEJWMEpwQV9URi10WVVFMk5aYWR3bGJjNGhqZGhST2dwVWFGa3l0UQ?oc=5</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>fox59.com</t>
+          <t>CNBC</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr"/>
@@ -10528,12 +11084,12 @@
       </c>
       <c r="Y13" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z13" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>attorney general</t>
         </is>
       </c>
       <c r="AA13" s="4" t="inlineStr">
@@ -10541,15 +11097,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr"/>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>962629bb4d8343d8b2df0a397aafd231</t>
+        </is>
+      </c>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>5d293840c452f2f47963b605</t>
+          <t>19ac0856711e24e1eb080c0e</t>
         </is>
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>5a39baed1e5af1babd36a364</t>
+          <t>00b3fe78af7ec9307af7c898</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr"/>
@@ -10562,7 +11122,11 @@
       <c r="AL13" s="4" t="inlineStr"/>
       <c r="AM13" s="4" t="inlineStr"/>
       <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr"/>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="inlineStr"/>
       <c r="AQ13" s="4" t="inlineStr"/>
       <c r="AR13" s="4" t="inlineStr"/>
@@ -10577,7 +11141,7 @@
       <c r="BA13" s="4" t="inlineStr"/>
       <c r="BB13" s="4" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>WBD</t>
         </is>
       </c>
       <c r="BC13" s="4" t="inlineStr">
@@ -10598,6 +11162,18 @@
         </is>
       </c>
       <c r="BH13" s="4" t="inlineStr"/>
+      <c r="BI13" s="4" t="inlineStr"/>
+      <c r="BJ13" s="4" t="inlineStr"/>
+      <c r="BK13" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -10612,12 +11188,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>CME Group Inc.</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -10627,7 +11203,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>CME CEO Spars With CFTC Chair About Prediction Market Oversight</t>
+          <t>INVESTOR ALERT: Pomerantz Law Firm Reminds Investors with Losses on their Investment in Pentair plc of Class Action Lawsuit and Upcoming Deadlines - PNR</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
@@ -10638,7 +11214,7 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>監管調查</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -10648,13 +11224,17 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -10664,7 +11244,7 @@
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>'-0.03</t>
+          <t>'-0.881</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr"/>
@@ -10678,12 +11258,12 @@
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPQl9ER0JjUC1UZ0lQUDhHTFl1dVZGUm9zZzEzd0lUVGRPcUxQSUhaU2h0ODhEd0xsX3ZoRjI3SUFqSWZlajNvdlB6QW9qckg3dnJaNHlqNU1TUTBjWndSSHVaLUlIbW1kRndjOXZ3Tnd3bkZBWlkzb3ZZdTFQbWpYWlRkbWNTdTVDZEJyVTRjMUdfbXJkNDRfRjRnZXJfNElhMDgtQTBwNGJPUkVEazVsRXhxaWs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxPOUZMNDZmM1lPNFFKelBOQ3kyRDBQOENLY2JHNE5VbWhBbmN3N0Z1aGFmTVdrcjF2aTJaTDlZSS15cVk2ckNLeU1haGpnLUFPb2xCb2FLb2Z3b1cwMjdBZDZ5WmoxdVNYcGYtMWJjRTFyRFMwOGhsa1ozLVhfU2hoUXdxdVYzMXpqelNXelFqclpEeGlzUXJqbkpUUnhaOWNfempCWWZvRHM5LWpORW41U3FYMHNPSnZQX2REVlJyV29MakdhNEZUQVZla01aREpEZ2czbWxEblZoX3BGdDNLcnR2UHRZOUl0RU1WTUJrdTNPOE5yMXdqc0kxSUU4OTdhc0lmNW1YLVBmWG9pblpSM19sMUlZSi1MbGhzUENKMTZfdl9LcGN3S3dtNTE1NW8?oc=5</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>Bloomberg.com</t>
+          <t>prnewswire.com</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr"/>
@@ -10694,12 +11274,12 @@
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_INVESTIGATION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
         <is>
-          <t>CFTC；FTC</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA14" s="4" t="inlineStr">
@@ -10707,15 +11287,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr"/>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>77c158a40ddc4258910ac1bc386e86a2</t>
+        </is>
+      </c>
       <c r="AC14" s="4" t="inlineStr">
         <is>
-          <t>a6314d7a313ab5ad737cc1a5</t>
+          <t>5ddf20be53114d48c44012a2</t>
         </is>
       </c>
       <c r="AD14" s="4" t="inlineStr">
         <is>
-          <t>4ce2f2951b07ed8eb8da64ae</t>
+          <t>aa0e0d1cde37f85e1e33d68d</t>
         </is>
       </c>
       <c r="AE14" s="4" t="inlineStr"/>
@@ -10728,7 +11312,11 @@
       <c r="AL14" s="4" t="inlineStr"/>
       <c r="AM14" s="4" t="inlineStr"/>
       <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr"/>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="4" t="inlineStr"/>
       <c r="AQ14" s="4" t="inlineStr"/>
       <c r="AR14" s="4" t="inlineStr"/>
@@ -10736,18 +11324,14 @@
       <c r="AT14" s="4" t="inlineStr"/>
       <c r="AU14" s="4" t="inlineStr"/>
       <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW14" s="4" t="inlineStr"/>
       <c r="AX14" s="4" t="inlineStr"/>
       <c r="AY14" s="4" t="inlineStr"/>
       <c r="AZ14" s="4" t="inlineStr"/>
       <c r="BA14" s="4" t="inlineStr"/>
       <c r="BB14" s="4" t="inlineStr">
         <is>
-          <t>CME</t>
+          <t>PNR</t>
         </is>
       </c>
       <c r="BC14" s="4" t="inlineStr">
@@ -10758,1569 +11342,387 @@
       <c r="BD14" s="4" t="inlineStr"/>
       <c r="BE14" s="4" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF14" s="4" t="inlineStr"/>
       <c r="BG14" s="4" t="inlineStr">
         <is>
-          <t>交易所目前名單</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH14" s="4" t="inlineStr"/>
+      <c r="BI14" s="4" t="inlineStr"/>
+      <c r="BJ14" s="4" t="inlineStr"/>
+      <c r="BK14" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>PepsiCo, Inc.</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Abbott in $670M settlement for some NEC infant formula claims (ABT:NYSE)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Over 100 PepsiCo employees in Columbia facing permanent layoffs, documents show</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>裁員或人力縮減</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="N15" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>'-0.492</t>
-        </is>
-      </c>
-      <c r="P15" s="4" t="inlineStr"/>
-      <c r="Q15" s="4" t="inlineStr"/>
-      <c r="R15" s="4" t="inlineStr"/>
-      <c r="S15" s="4" t="inlineStr"/>
-      <c r="T15" s="4" t="inlineStr">
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>'-0.962</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNcWMxOVUxR0pMYkkwVmlQaGd3eUR0NnZkT2RoWnF2RzNVS1dVSlNHVVlQd1hfa05nN2p4MUFjRGdET2x2MTlvdW51cFpXVW1sWTRfNkRIZ0hVTjFtOHJuTnE2LVBBdWNHYWlLeXQ4b1dzUmlOWnRVcGRhOXV5cWkxbjdOcW00UVExWmVZQlA0dXc5NFpCU1E?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr"/>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmJjaEc5ZW93MFFVY0tnUmVZQ0REMlJ2YkY5YkgyVm16d0kyRVVnNFZ3dW9UYmJ1aDQ4MXFvMHlfOURQVll6ajN4Nm90ejhQT3dHNWdqbmc1RTNqWEh6SU9PQjlsVDZjbWZzaXExRVR5Qzg2ZU5RTkZNbW9TWlJ4SjBsRUVwT3VUdlpiUWNobEtCMUJpNlo0NFQ0VENsZE5pZmNQX0JXeGVqOE9Qb0HSAcIBQVVfeXFMTjVVSDAxVnNlZUpSbEtwc3hOVWlLVW41QmlMaERyZkg2eDk3MHNNaWJlb2gzc19SOTByNG91aG05RTI0aHVNM3hteTk5VXM5YmkyUV8wZkpVOTdkS2JjaVdWR181Qndqc2NTa2swbWJJeXQ3RlZkeTVOYlBoUlhvRndvTVk0bkZBLWtUMWRHUlRrVDdfVklJSERjM090WVRyUjhwZEV5WncySHRNWV9BNGFmd3h0ZWo1OFdwMEdyOC0tYVE?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>WIS News 10</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>WORKFORCE_REDUCTION</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr"/>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>1f0369a48bb25dc74096908b</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>202eba2fa538a72147f07e7f</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr"/>
-      <c r="AF15" s="4" t="inlineStr"/>
-      <c r="AG15" s="4" t="inlineStr"/>
-      <c r="AH15" s="4" t="inlineStr"/>
-      <c r="AI15" s="4" t="inlineStr"/>
-      <c r="AJ15" s="4" t="inlineStr"/>
-      <c r="AK15" s="4" t="inlineStr"/>
-      <c r="AL15" s="4" t="inlineStr"/>
-      <c r="AM15" s="4" t="inlineStr"/>
-      <c r="AN15" s="4" t="inlineStr"/>
-      <c r="AO15" s="4" t="inlineStr"/>
-      <c r="AP15" s="4" t="inlineStr"/>
-      <c r="AQ15" s="4" t="inlineStr"/>
-      <c r="AR15" s="4" t="inlineStr"/>
-      <c r="AS15" s="4" t="inlineStr"/>
-      <c r="AT15" s="4" t="inlineStr"/>
-      <c r="AU15" s="4" t="inlineStr"/>
-      <c r="AV15" s="4" t="inlineStr"/>
-      <c r="AW15" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX15" s="4" t="inlineStr"/>
-      <c r="AY15" s="4" t="inlineStr"/>
-      <c r="AZ15" s="4" t="inlineStr"/>
-      <c r="BA15" s="4" t="inlineStr"/>
-      <c r="BB15" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC15" s="4" t="inlineStr">
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>197a030e866462b53c92be76</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>094940ea9bbef65029c0ac7d</t>
+        </is>
+      </c>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr"/>
+      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AU15" s="3" t="inlineStr"/>
+      <c r="AV15" s="3" t="inlineStr"/>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr"/>
+      <c r="AY15" s="3" t="inlineStr"/>
+      <c r="AZ15" s="3" t="inlineStr"/>
+      <c r="BA15" s="3" t="inlineStr"/>
+      <c r="BB15" s="3" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="BC15" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="4" t="inlineStr"/>
-      <c r="BE15" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF15" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG15" s="4" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH15" s="4" t="inlineStr"/>
+      <c r="BD15" s="3" t="inlineStr"/>
+      <c r="BE15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG15" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH15" s="3" t="inlineStr"/>
+      <c r="BI15" s="3" t="inlineStr"/>
+      <c r="BJ15" s="3" t="inlineStr"/>
+      <c r="BK15" s="3" t="inlineStr"/>
+      <c r="BL15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>California Attorney General Rob Bonta: Paramount-WBD lawsuit is a 'black-and-white' antitrust case</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>International Business Machines Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20T04:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>IBM’s 2026 Data Breach Report: Houston, We Have A Problem</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>資料外洩</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="N16" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>'-0.552</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr"/>
-      <c r="Q16" s="4" t="inlineStr"/>
-      <c r="R16" s="4" t="inlineStr"/>
-      <c r="S16" s="4" t="inlineStr"/>
-      <c r="T16" s="4" t="inlineStr">
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>'-0.946</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVGFJMndFT0FkV2Zfb1I3Qy1hQWFGV2tWVzJONzM2ODFLR0l3bjVhX3dCWVo4dnlMaERVYWhDVTB4dTlUNG1TMHJFSjZEcUgyR3kxSFhIb0tnWDVFRDVjeEcyTDBnV0ZWME5BMmxPbHl6NlR2Y2p0R1hkWDVtcDJ5dmJBcEJWMEpwQV9URi10WVVFMk5aYWR3bGJjNGhqZGhST2dwVWFGa3l0UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr"/>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUXZUWlJkaXVxNldYVjRSMXowQ0xFTWw2SXcwdVppbUFsR05qWVFIejc3eXNoMkRSWnVxaVdtS0RjcC1DVVZtN0FxLTJMNHlzMEdpS3IxSUhUMW5DcmMxbW5SUkl6VF8wZnFaM2Ytd1gzR3AzNE1CR3J3djQxNlE5Y2M0X0N0Z0xJN21ZTEtYYXU?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Above the Law</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>DATA_BREACH</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>19ac0856711e24e1eb080c0e</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>00b3fe78af7ec9307af7c898</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr"/>
-      <c r="AF16" s="4" t="inlineStr"/>
-      <c r="AG16" s="4" t="inlineStr"/>
-      <c r="AH16" s="4" t="inlineStr"/>
-      <c r="AI16" s="4" t="inlineStr"/>
-      <c r="AJ16" s="4" t="inlineStr"/>
-      <c r="AK16" s="4" t="inlineStr"/>
-      <c r="AL16" s="4" t="inlineStr"/>
-      <c r="AM16" s="4" t="inlineStr"/>
-      <c r="AN16" s="4" t="inlineStr"/>
-      <c r="AO16" s="4" t="inlineStr"/>
-      <c r="AP16" s="4" t="inlineStr"/>
-      <c r="AQ16" s="4" t="inlineStr"/>
-      <c r="AR16" s="4" t="inlineStr"/>
-      <c r="AS16" s="4" t="inlineStr"/>
-      <c r="AT16" s="4" t="inlineStr"/>
-      <c r="AU16" s="4" t="inlineStr"/>
-      <c r="AV16" s="4" t="inlineStr"/>
-      <c r="AW16" s="4" t="inlineStr"/>
-      <c r="AX16" s="4" t="inlineStr"/>
-      <c r="AY16" s="4" t="inlineStr"/>
-      <c r="AZ16" s="4" t="inlineStr"/>
-      <c r="BA16" s="4" t="inlineStr"/>
-      <c r="BB16" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC16" s="4" t="inlineStr">
+      <c r="AB16" s="3" t="inlineStr"/>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>2ff2c3663d180b21905740d5</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>b5fb7ce9cc34eee18630b78a</t>
+        </is>
+      </c>
+      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr"/>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr"/>
+      <c r="AM16" s="3" t="inlineStr"/>
+      <c r="AN16" s="3" t="inlineStr"/>
+      <c r="AO16" s="3" t="inlineStr"/>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr"/>
+      <c r="AS16" s="3" t="inlineStr"/>
+      <c r="AT16" s="3" t="inlineStr"/>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr"/>
+      <c r="AY16" s="3" t="inlineStr"/>
+      <c r="AZ16" s="3" t="inlineStr"/>
+      <c r="BA16" s="3" t="inlineStr"/>
+      <c r="BB16" s="3" t="inlineStr">
+        <is>
+          <t>IBM</t>
+        </is>
+      </c>
+      <c r="BC16" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD16" s="4" t="inlineStr"/>
-      <c r="BE16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF16" s="4" t="inlineStr"/>
-      <c r="BG16" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>INVESTOR ALERT: Pomerantz Law Firm Reminds Investors with Losses on their Investment in Pentair plc of Class Action Lawsuit and Upcoming Deadlines - PNR</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>'-0.881</t>
-        </is>
-      </c>
-      <c r="P17" s="4" t="inlineStr"/>
-      <c r="Q17" s="4" t="inlineStr"/>
-      <c r="R17" s="4" t="inlineStr"/>
-      <c r="S17" s="4" t="inlineStr"/>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxPOUZMNDZmM1lPNFFKelBOQ3kyRDBQOENLY2JHNE5VbWhBbmN3N0Z1aGFmTVdrcjF2aTJaTDlZSS15cVk2ckNLeU1haGpnLUFPb2xCb2FLb2Z3b1cwMjdBZDZ5WmoxdVNYcGYtMWJjRTFyRFMwOGhsa1ozLVhfU2hoUXdxdVYzMXpqelNXelFqclpEeGlzUXJqbkpUUnhaOWNfempCWWZvRHM5LWpORW41U3FYMHNPSnZQX2REVlJyV29MakdhNEZUQVZla01aREpEZ2czbWxEblZoX3BGdDNLcnR2UHRZOUl0RU1WTUJrdTNPOE5yMXdqc0kxSUU4OTdhc0lmNW1YLVBmWG9pblpSM19sMUlZSi1MbGhzUENKMTZfdl9LcGN3S3dtNTE1NW8?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>prnewswire.com</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr"/>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="4" t="inlineStr"/>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>5ddf20be53114d48c44012a2</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>aa0e0d1cde37f85e1e33d68d</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr"/>
-      <c r="AF17" s="4" t="inlineStr"/>
-      <c r="AG17" s="4" t="inlineStr"/>
-      <c r="AH17" s="4" t="inlineStr"/>
-      <c r="AI17" s="4" t="inlineStr"/>
-      <c r="AJ17" s="4" t="inlineStr"/>
-      <c r="AK17" s="4" t="inlineStr"/>
-      <c r="AL17" s="4" t="inlineStr"/>
-      <c r="AM17" s="4" t="inlineStr"/>
-      <c r="AN17" s="4" t="inlineStr"/>
-      <c r="AO17" s="4" t="inlineStr"/>
-      <c r="AP17" s="4" t="inlineStr"/>
-      <c r="AQ17" s="4" t="inlineStr"/>
-      <c r="AR17" s="4" t="inlineStr"/>
-      <c r="AS17" s="4" t="inlineStr"/>
-      <c r="AT17" s="4" t="inlineStr"/>
-      <c r="AU17" s="4" t="inlineStr"/>
-      <c r="AV17" s="4" t="inlineStr"/>
-      <c r="AW17" s="4" t="inlineStr"/>
-      <c r="AX17" s="4" t="inlineStr"/>
-      <c r="AY17" s="4" t="inlineStr"/>
-      <c r="AZ17" s="4" t="inlineStr"/>
-      <c r="BA17" s="4" t="inlineStr"/>
-      <c r="BB17" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC17" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD17" s="4" t="inlineStr"/>
-      <c r="BE17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF17" s="4" t="inlineStr"/>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>CME Group Inc.</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>CFTC Innovation Advisory Committee meeting: CME Group CEO Warns About Prediction Market Listings Open to Manipulation</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>'-0.894</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="inlineStr"/>
-      <c r="Q18" s="4" t="inlineStr"/>
-      <c r="R18" s="4" t="inlineStr"/>
-      <c r="S18" s="4" t="inlineStr"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi-AFBVV95cUxOR1FjYm1fS2xld2hJZFlZVGJMaFd4OXJUajJsX0xYZEwtcDZEZS1EUkNjdi1qZUtQQTNyRVozUVR3TkNYbHU4RV9GRTdtbTFPMEZlQV9HbUdSb01MVmRwdVJBRUI2VkVQZm9GMlRSalJsZWF0cXppUzJnY2pfNlpmcVdsYnZHWVhnOFBhekdFZGVoOU56b1QwZ3JZeGd5UF9xcjFRZldKN1lQWWFHdlFKX2FXSlUzLVV5OXJrOXRpT1VvS2tuSUR1VThiSm1qdVBzSHE5VXIzR1huakpDWGpnZlcyS1VEejBBR0tUUXBWek9aMzNmY3MxVg?oc=5</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>Crowdfund Insider</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr"/>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>CFTC；FTC</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="4" t="inlineStr"/>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>8c37fce9611dc02868f91729</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="inlineStr">
-        <is>
-          <t>29ca53ec6f51746b22cb1b98</t>
-        </is>
-      </c>
-      <c r="AE18" s="4" t="inlineStr"/>
-      <c r="AF18" s="4" t="inlineStr"/>
-      <c r="AG18" s="4" t="inlineStr"/>
-      <c r="AH18" s="4" t="inlineStr"/>
-      <c r="AI18" s="4" t="inlineStr"/>
-      <c r="AJ18" s="4" t="inlineStr"/>
-      <c r="AK18" s="4" t="inlineStr"/>
-      <c r="AL18" s="4" t="inlineStr"/>
-      <c r="AM18" s="4" t="inlineStr"/>
-      <c r="AN18" s="4" t="inlineStr"/>
-      <c r="AO18" s="4" t="inlineStr"/>
-      <c r="AP18" s="4" t="inlineStr"/>
-      <c r="AQ18" s="4" t="inlineStr"/>
-      <c r="AR18" s="4" t="inlineStr"/>
-      <c r="AS18" s="4" t="inlineStr"/>
-      <c r="AT18" s="4" t="inlineStr"/>
-      <c r="AU18" s="4" t="inlineStr"/>
-      <c r="AV18" s="4" t="inlineStr"/>
-      <c r="AW18" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX18" s="4" t="inlineStr"/>
-      <c r="AY18" s="4" t="inlineStr"/>
-      <c r="AZ18" s="4" t="inlineStr"/>
-      <c r="BA18" s="4" t="inlineStr"/>
-      <c r="BB18" s="4" t="inlineStr">
-        <is>
-          <t>CME</t>
-        </is>
-      </c>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="inlineStr"/>
-      <c r="BE18" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF18" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG18" s="4" t="inlineStr">
+      <c r="BD16" s="3" t="inlineStr"/>
+      <c r="BE16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG16" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH18" s="4" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>Dominion Energy</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Declaring ‘economic D-Day,’ Trump says any country trading with Iran will be sanctioned</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>0.064</t>
-        </is>
-      </c>
-      <c r="P19" s="4" t="inlineStr"/>
-      <c r="Q19" s="4" t="inlineStr"/>
-      <c r="R19" s="4" t="inlineStr"/>
-      <c r="S19" s="4" t="inlineStr"/>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUW9hZVlPQXhRVER0YkNDM01PVUpFYUtEWFBSUFVQcWE5TDgxOTNPSnVzeThVYldZWVZqYUhSZVRZb0hvT200ZjZ3WW9UUmV4OVc0Q21mQ0ZkMXBmZlZWNjhKaE53akF2YjFxaW5MM3d1SVJ1TVBwRXBaanhsQk1BdDRMZW00YVdHSEpYSjA2OUJLaWVDdV94aGJCOGRRVndTc1pCTFNKWnRnSlJfdWRBREhrRzJIQdIBuwFBVV95cUxNVlYwaUJHaWRocnlZbUllTDdlS1pGZmhYd3RyUTN2STZmeXpTLWZLalRsbjJNYldQNFp4eUpWd3dmWHBNTXMxZTFjOWtlR01HOFRSX1RJSmNad2p1dGw2ZWgxb0ZHbFJ0QjR2aEVDWS0ycE05QnRTLUhnbzFtWUJNeHo1ZVV5alZUaHVzdFFDYm9xZjh3cWtiR3Y1RHJXZ0FHN1VRNU13SG5XUzAzNmxZT1Zlc0RKTGEyaHA0?oc=5</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>The Times of Israel</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr"/>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>sanctioned</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="4" t="inlineStr"/>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>85cb731df7d7894e88040b4d</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>65dd2640523a4c6c2f9ce79a</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr"/>
-      <c r="AF19" s="4" t="inlineStr"/>
-      <c r="AG19" s="4" t="inlineStr"/>
-      <c r="AH19" s="4" t="inlineStr"/>
-      <c r="AI19" s="4" t="inlineStr"/>
-      <c r="AJ19" s="4" t="inlineStr"/>
-      <c r="AK19" s="4" t="inlineStr"/>
-      <c r="AL19" s="4" t="inlineStr"/>
-      <c r="AM19" s="4" t="inlineStr"/>
-      <c r="AN19" s="4" t="inlineStr"/>
-      <c r="AO19" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP19" s="4" t="inlineStr"/>
-      <c r="AQ19" s="4" t="inlineStr"/>
-      <c r="AR19" s="4" t="inlineStr"/>
-      <c r="AS19" s="4" t="inlineStr"/>
-      <c r="AT19" s="4" t="inlineStr"/>
-      <c r="AU19" s="4" t="inlineStr"/>
-      <c r="AV19" s="4" t="inlineStr"/>
-      <c r="AW19" s="4" t="inlineStr"/>
-      <c r="AX19" s="4" t="inlineStr"/>
-      <c r="AY19" s="4" t="inlineStr"/>
-      <c r="AZ19" s="4" t="inlineStr"/>
-      <c r="BA19" s="4" t="inlineStr"/>
-      <c r="BB19" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="BC19" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD19" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="BE19" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF19" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG19" s="4" t="inlineStr"/>
-      <c r="BH19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>PepsiCo, Inc.</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Over 100 PepsiCo employees in Columbia facing permanent layoffs, documents show</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>'-0.962</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmJjaEc5ZW93MFFVY0tnUmVZQ0REMlJ2YkY5YkgyVm16d0kyRVVnNFZ3dW9UYmJ1aDQ4MXFvMHlfOURQVll6ajN4Nm90ejhQT3dHNWdqbmc1RTNqWEh6SU9PQjlsVDZjbWZzaXExRVR5Qzg2ZU5RTkZNbW9TWlJ4SjBsRUVwT3VUdlpiUWNobEtCMUJpNlo0NFQ0VENsZE5pZmNQX0JXeGVqOE9Qb0HSAcIBQVVfeXFMTjVVSDAxVnNlZUpSbEtwc3hOVWlLVW41QmlMaERyZkg2eDk3MHNNaWJlb2gzc19SOTByNG91aG05RTI0aHVNM3hteTk5VXM5YmkyUV8wZkpVOTdkS2JjaVdWR181Qndqc2NTa2swbWJJeXQ3RlZkeTVOYlBoUlhvRndvTVk0bkZBLWtUMWRHUlRrVDdfVklJSERjM090WVRyUjhwZEV5WncySHRNWV9BNGFmd3h0ZWo1OFdwMEdyOC0tYVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V20" s="3" t="inlineStr">
-        <is>
-          <t>WIS News 10</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="3" t="inlineStr">
-        <is>
-          <t>197a030e866462b53c92be76</t>
-        </is>
-      </c>
-      <c r="AD20" s="3" t="inlineStr">
-        <is>
-          <t>094940ea9bbef65029c0ac7d</t>
-        </is>
-      </c>
-      <c r="AE20" s="3" t="inlineStr"/>
-      <c r="AF20" s="3" t="inlineStr"/>
-      <c r="AG20" s="3" t="inlineStr"/>
-      <c r="AH20" s="3" t="inlineStr"/>
-      <c r="AI20" s="3" t="inlineStr"/>
-      <c r="AJ20" s="3" t="inlineStr"/>
-      <c r="AK20" s="3" t="inlineStr"/>
-      <c r="AL20" s="3" t="inlineStr"/>
-      <c r="AM20" s="3" t="inlineStr"/>
-      <c r="AN20" s="3" t="inlineStr"/>
-      <c r="AO20" s="3" t="inlineStr"/>
-      <c r="AP20" s="3" t="inlineStr"/>
-      <c r="AQ20" s="3" t="inlineStr"/>
-      <c r="AR20" s="3" t="inlineStr"/>
-      <c r="AS20" s="3" t="inlineStr"/>
-      <c r="AT20" s="3" t="inlineStr"/>
-      <c r="AU20" s="3" t="inlineStr"/>
-      <c r="AV20" s="3" t="inlineStr"/>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX20" s="3" t="inlineStr"/>
-      <c r="AY20" s="3" t="inlineStr"/>
-      <c r="AZ20" s="3" t="inlineStr"/>
-      <c r="BA20" s="3" t="inlineStr"/>
-      <c r="BB20" s="3" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="BC20" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD20" s="3" t="inlineStr"/>
-      <c r="BE20" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF20" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG20" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T06:07:05+08:00</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Colorado attorney general sues ​ICE detention center operator ​i​n tuberculosis ​case</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr"/>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>'-0.923</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr"/>
-      <c r="Q21" s="4" t="inlineStr"/>
-      <c r="R21" s="4" t="inlineStr"/>
-      <c r="S21" s="4" t="inlineStr"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTE9mTl81MjBxWW1ncEJ6S2hWNUFLdzdZaDduOElPc1FhTmJ0VHlQUHViOVNQWThCWC1JemU1QkVmbE05d2s4V3N5Rm9NWGwxRFdoUzAtS2JhQkdLNWZ6bkJDS19PdWtQaF9aanM5M1R1dWJkeTdTeFRXZk1QOA?oc=5</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>Colorado Newsline</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr"/>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="4" t="inlineStr"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>72cca324c95efb8846f49b57</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="inlineStr">
-        <is>
-          <t>432e70cfc3cd017e4c677aa0</t>
-        </is>
-      </c>
-      <c r="AE21" s="4" t="inlineStr"/>
-      <c r="AF21" s="4" t="inlineStr"/>
-      <c r="AG21" s="4" t="inlineStr"/>
-      <c r="AH21" s="4" t="inlineStr"/>
-      <c r="AI21" s="4" t="inlineStr"/>
-      <c r="AJ21" s="4" t="inlineStr"/>
-      <c r="AK21" s="4" t="inlineStr"/>
-      <c r="AL21" s="4" t="inlineStr"/>
-      <c r="AM21" s="4" t="inlineStr"/>
-      <c r="AN21" s="4" t="inlineStr"/>
-      <c r="AO21" s="4" t="inlineStr"/>
-      <c r="AP21" s="4" t="inlineStr"/>
-      <c r="AQ21" s="4" t="inlineStr"/>
-      <c r="AR21" s="4" t="inlineStr"/>
-      <c r="AS21" s="4" t="inlineStr"/>
-      <c r="AT21" s="4" t="inlineStr"/>
-      <c r="AU21" s="4" t="inlineStr"/>
-      <c r="AV21" s="4" t="inlineStr"/>
-      <c r="AW21" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX21" s="4" t="inlineStr"/>
-      <c r="AY21" s="4" t="inlineStr"/>
-      <c r="AZ21" s="4" t="inlineStr"/>
-      <c r="BA21" s="4" t="inlineStr"/>
-      <c r="BB21" s="4" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="BC21" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD21" s="4" t="inlineStr"/>
-      <c r="BE21" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF21" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG21" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Delta Air Lines</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T05:13:58+08:00</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>美國聯邦貿易委員會（FTC）正考慮要求披露個性化定價</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O22" s="4" t="inlineStr"/>
-      <c r="P22" s="4" t="inlineStr"/>
-      <c r="Q22" s="4" t="inlineStr"/>
-      <c r="R22" s="4" t="inlineStr"/>
-      <c r="S22" s="4" t="inlineStr"/>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DAL/news/</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr"/>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="4" t="inlineStr"/>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>5a8dc1a140bbb656bc23cba9</t>
-        </is>
-      </c>
-      <c r="AD22" s="4" t="inlineStr">
-        <is>
-          <t>22a56251dfb3f01a27778045</t>
-        </is>
-      </c>
-      <c r="AE22" s="4" t="inlineStr"/>
-      <c r="AF22" s="4" t="inlineStr"/>
-      <c r="AG22" s="4" t="inlineStr"/>
-      <c r="AH22" s="4" t="inlineStr"/>
-      <c r="AI22" s="4" t="inlineStr"/>
-      <c r="AJ22" s="4" t="inlineStr"/>
-      <c r="AK22" s="4" t="inlineStr"/>
-      <c r="AL22" s="4" t="inlineStr"/>
-      <c r="AM22" s="4" t="inlineStr"/>
-      <c r="AN22" s="4" t="inlineStr"/>
-      <c r="AO22" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP22" s="4" t="inlineStr"/>
-      <c r="AQ22" s="4" t="inlineStr"/>
-      <c r="AR22" s="4" t="inlineStr"/>
-      <c r="AS22" s="4" t="inlineStr"/>
-      <c r="AT22" s="4" t="inlineStr"/>
-      <c r="AU22" s="4" t="inlineStr"/>
-      <c r="AV22" s="4" t="inlineStr"/>
-      <c r="AW22" s="4" t="inlineStr"/>
-      <c r="AX22" s="4" t="inlineStr"/>
-      <c r="AY22" s="4" t="inlineStr"/>
-      <c r="AZ22" s="4" t="inlineStr"/>
-      <c r="BA22" s="4" t="inlineStr"/>
-      <c r="BB22" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="BC22" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD22" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="BE22" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF22" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG22" s="4" t="inlineStr"/>
-      <c r="BH22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20T04:01:00+08:00</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>IBM’s 2026 Data Breach Report: Houston, We Have A Problem</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>'-0.946</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="3" t="inlineStr"/>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUXZUWlJkaXVxNldYVjRSMXowQ0xFTWw2SXcwdVppbUFsR05qWVFIejc3eXNoMkRSWnVxaVdtS0RjcC1DVVZtN0FxLTJMNHlzMEdpS3IxSUhUMW5DcmMxbW5SUkl6VF8wZnFaM2Ytd1gzR3AzNE1CR3J3djQxNlE5Y2M0X0N0Z0xJN21ZTEtYYXU?oc=5</t>
-        </is>
-      </c>
-      <c r="V23" s="3" t="inlineStr">
-        <is>
-          <t>Above the Law</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA23" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="3" t="inlineStr">
-        <is>
-          <t>2ff2c3663d180b21905740d5</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>b5fb7ce9cc34eee18630b78a</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="inlineStr"/>
-      <c r="AF23" s="3" t="inlineStr"/>
-      <c r="AG23" s="3" t="inlineStr"/>
-      <c r="AH23" s="3" t="inlineStr"/>
-      <c r="AI23" s="3" t="inlineStr"/>
-      <c r="AJ23" s="3" t="inlineStr"/>
-      <c r="AK23" s="3" t="inlineStr"/>
-      <c r="AL23" s="3" t="inlineStr"/>
-      <c r="AM23" s="3" t="inlineStr"/>
-      <c r="AN23" s="3" t="inlineStr"/>
-      <c r="AO23" s="3" t="inlineStr"/>
-      <c r="AP23" s="3" t="inlineStr"/>
-      <c r="AQ23" s="3" t="inlineStr"/>
-      <c r="AR23" s="3" t="inlineStr"/>
-      <c r="AS23" s="3" t="inlineStr"/>
-      <c r="AT23" s="3" t="inlineStr"/>
-      <c r="AU23" s="3" t="inlineStr"/>
-      <c r="AV23" s="3" t="inlineStr"/>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX23" s="3" t="inlineStr"/>
-      <c r="AY23" s="3" t="inlineStr"/>
-      <c r="AZ23" s="3" t="inlineStr"/>
-      <c r="BA23" s="3" t="inlineStr"/>
-      <c r="BB23" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC23" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD23" s="3" t="inlineStr"/>
-      <c r="BE23" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF23" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG23" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH23" s="3" t="inlineStr"/>
+      <c r="BH16" s="3" t="inlineStr"/>
+      <c r="BI16" s="3" t="inlineStr"/>
+      <c r="BJ16" s="3" t="inlineStr"/>
+      <c r="BK16" s="3" t="inlineStr"/>
+      <c r="BL16" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH23"/>
+  <autoFilter ref="A1:BL16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12331,7 +11733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12394,6 +11796,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12695,6 +12101,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -12871,6 +12297,10 @@
       </c>
       <c r="BG2" s="2" t="inlineStr"/>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -13037,6 +12467,10 @@
       <c r="BF3" s="2" t="inlineStr"/>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -13211,6 +12645,10 @@
       </c>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -13385,180 +12823,180 @@
       </c>
       <c r="BG5" s="3" t="inlineStr"/>
       <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr"/>
+      <c r="BL5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Dominion Energy</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fastenal</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Declaring ‘economic D-Day,’ Trump says any country trading with Iran will be sanctioned</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Fast-spreading wildfire threatens structures near China Spring</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>天災</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.064</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>'-0.909</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNUW9hZVlPQXhRVER0YkNDM01PVUpFYUtEWFBSUFVQcWE5TDgxOTNPSnVzeThVYldZWVZqYUhSZVRZb0hvT200ZjZ3WW9UUmV4OVc0Q21mQ0ZkMXBmZlZWNjhKaE53akF2YjFxaW5MM3d1SVJ1TVBwRXBaanhsQk1BdDRMZW00YVdHSEpYSjA2OUJLaWVDdV94aGJCOGRRVndTc1pCTFNKWnRnSlJfdWRBREhrRzJIQdIBuwFBVV95cUxNVlYwaUJHaWRocnlZbUllTDdlS1pGZmhYd3RyUTN2STZmeXpTLWZLalRsbjJNYldQNFp4eUpWd3dmWHBNTXMxZTFjOWtlR01HOFRSX1RJSmNad2p1dGw2ZWgxb0ZHbFJ0QjR2aEVDWS0ycE05QnRTLUhnbzFtWUJNeHo1ZVV5alZUaHVzdFFDYm9xZjh3cWtiR3Y1RHJXZ0FHN1VRNU13SG5XUzAzNmxZT1Zlc0RKTGEyaHA0?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>The Times of Israel</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>sanctioned</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOUS15ckRkc1VKWWstYjdFOWZnbmlTWE9pQWNhZ0swM3hzN1VDSzJpX01tQU9wT1QybVVWc2tSbTRuQjN6Qm1DT0NIUlFJQWc0SElvVWZXdHY1djNTYWZEU3Bxa0U4WDNOMFpjN2NuQ0IzT1pUZzNkVGJMd0V2TmV0TVlOaWVaQ1ZwQldwLWJ5dFlOR0taTl93LVBWZFVSV0pTRUczUmhxd3BWaFFkSjlEWFItOXJJWGl0MWVLdXpMYXd1VFVZeHVLN2FHOExfSnlIQzM1RDJWWWs1LXM?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>KCENTV.com</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>NATURAL_DISASTER</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>wildfire</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>85cb731df7d7894e88040b4d</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>65dd2640523a4c6c2f9ce79a</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>710d96aeafcd9dd89a0947b6</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr">
+        <is>
+          <t>d1b990d8b8cd706ccea45a4c</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="AP6" s="2" t="inlineStr"/>
+      <c r="AQ6" s="2" t="inlineStr"/>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr"/>
+      <c r="AT6" s="2" t="inlineStr"/>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
+      <c r="AX6" s="2" t="inlineStr"/>
+      <c r="AY6" s="2" t="inlineStr"/>
+      <c r="AZ6" s="2" t="inlineStr"/>
+      <c r="BA6" s="2" t="inlineStr"/>
+      <c r="BB6" s="2" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="BC6" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="4" t="inlineStr"/>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BD6" s="2" t="inlineStr">
+        <is>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="BE6" s="2" t="inlineStr"/>
+      <c r="BF6" s="2" t="inlineStr"/>
+      <c r="BG6" s="2" t="inlineStr"/>
+      <c r="BH6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BJ6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr"/>
+      <c r="BL6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -13584,7 +13022,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Fast-spreading wildfire threatens structures near China Spring</t>
+          <t>WATCH: New video shows fast-moving water flood Metro bus during July storms</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
@@ -13625,7 +13063,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>'-0.909</t>
+          <t>0.037</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr"/>
@@ -13639,12 +13077,12 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOUS15ckRkc1VKWWstYjdFOWZnbmlTWE9pQWNhZ0swM3hzN1VDSzJpX01tQU9wT1QybVVWc2tSbTRuQjN6Qm1DT0NIUlFJQWc0SElvVWZXdHY1djNTYWZEU3Bxa0U4WDNOMFpjN2NuQ0IzT1pUZzNkVGJMd0V2TmV0TVlOaWVaQ1ZwQldwLWJ5dFlOR0taTl93LVBWZFVSV0pTRUczUmhxd3BWaFFkSjlEWFItOXJJWGl0MWVLdXpMYXd1VFVZeHVLN2FHOExfSnlIQzM1RDJWWWs1LXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQRWxxRV9TdUtBbzFKaWNmLVV1TmRINlRVNmFhUVNTNFp3bzRnektMNndwcERXV2JuYTQ2dUltN05paWJBaWJJS0pEampBLWk5cnJEVXpxcjk3RDRqVVV0NU94M3JEQkFSdjR5Q0pNSlM1cHkzeWNyR3kxd1llcXB2b3htdEtndjNud0Focg?oc=5</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>KCENTV.com</t>
+          <t>WLWT</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr"/>
@@ -13660,7 +13098,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>wildfire</t>
+          <t>flood</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -13671,12 +13109,12 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>710d96aeafcd9dd89a0947b6</t>
+          <t>ba8d55b8d4bcb962a9c92d34</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>d1b990d8b8cd706ccea45a4c</t>
+          <t>db070a980a254deb9b99b516</t>
         </is>
       </c>
       <c r="AE7" s="2" t="inlineStr"/>
@@ -13725,6 +13163,10 @@
       <c r="BF7" s="2" t="inlineStr"/>
       <c r="BG7" s="2" t="inlineStr"/>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -13740,7 +13182,7 @@
       <c r="C8" s="2" t="inlineStr"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Fastenal</t>
+          <t>O’Reilly Automotive</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -13750,7 +13192,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>WATCH: New video shows fast-moving water flood Metro bus during July storms</t>
+          <t>Former Marines Orly Guteza reportedly detailed in his recantation how his former statements had been forced upon him so he could link Leyte 1st District Rep. Martin Romualdez to the flood control controversy. https://tinyurl.com/5cyhaehr</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
@@ -13791,7 +13233,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>'-0.233</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr"/>
@@ -13805,12 +13247,12 @@
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQRWxxRV9TdUtBbzFKaWNmLVV1TmRINlRVNmFhUVNTNFp3bzRnektMNndwcERXV2JuYTQ2dUltN05paWJBaWJJS0pEampBLWk5cnJEVXpxcjk3RDRqVVV0NU94M3JEQkFSdjR5Q0pNSlM1cHkzeWNyR3kxd1llcXB2b3htdEtndjNud0Focg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPU0JWZ1Vfd01oa0VCTGtRVlFuTnZRMHJDNnZPblJoYmF2U2htQU1HSEFYOGs2ZjlxWUJKemR4X2pxNXRfbWFZdTFWZXZKZ0VrSEdXRGtDN1V6TmZESjNwdnFnLWFwY3piOGJRSGNxSVJYaE1VNFB2Nm1JV2U4eW5nN3ZhVWdpZVVrUjRJck5SX1E2VDZ3TW9nZEZwLVYxMEduOEpOLXl3UXh1eks3V2lINWNveENDQnRvb0E3R0dkVW5yTkhjRjd1X2VHd2dpd0hxRWV3ZEJBbWt1VlJE?oc=5</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>WLWT</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr"/>
@@ -13837,12 +13279,12 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>ba8d55b8d4bcb962a9c92d34</t>
+          <t>815071602ea7a305ed23b696</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>db070a980a254deb9b99b516</t>
+          <t>b52b9dfcd55a0b7eb55b1761</t>
         </is>
       </c>
       <c r="AE8" s="2" t="inlineStr"/>
@@ -13874,7 +13316,7 @@
       <c r="BA8" s="2" t="inlineStr"/>
       <c r="BB8" s="2" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>ORLY</t>
         </is>
       </c>
       <c r="BC8" s="2" t="inlineStr">
@@ -13884,13 +13326,25 @@
       </c>
       <c r="BD8" s="2" t="inlineStr">
         <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BE8" s="2" t="inlineStr"/>
-      <c r="BF8" s="2" t="inlineStr"/>
+          <t>ORLY</t>
+        </is>
+      </c>
+      <c r="BE8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
       <c r="BG8" s="2" t="inlineStr"/>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -13906,7 +13360,7 @@
       <c r="C9" s="2" t="inlineStr"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>O’Reilly Automotive</t>
+          <t>Fastenal</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -13916,7 +13370,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Former Marines Orly Guteza reportedly detailed in his recantation how his former statements had been forced upon him so he could link Leyte 1st District Rep. Martin Romualdez to the flood control controversy. https://tinyurl.com/5cyhaehr</t>
+          <t>Fast-moving wildfires leave forests less able to recover, Western study finds</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -13957,7 +13411,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>'-0.233</t>
+          <t>'-0.849</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr"/>
@@ -13971,12 +13425,12 @@
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPU0JWZ1Vfd01oa0VCTGtRVlFuTnZRMHJDNnZPblJoYmF2U2htQU1HSEFYOGs2ZjlxWUJKemR4X2pxNXRfbWFZdTFWZXZKZ0VrSEdXRGtDN1V6TmZESjNwdnFnLWFwY3piOGJRSGNxSVJYaE1VNFB2Nm1JV2U4eW5nN3ZhVWdpZVVrUjRJck5SX1E2VDZ3TW9nZEZwLVYxMEduOEpOLXl3UXh1eks3V2lINWNveENDQnRvb0E3R0dkVW5yTkhjRjd1X2VHd2dpd0hxRWV3ZEJBbWt1VlJE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNSHVNc042bjFPcmNacmpBRDhJZUVMaEk2clhXSnk5U1pvWTMwN0pqN1hxbkdsMEhHc09LMEdVRlhwMkdmUDlOTXZZYUU3SzlfSTRsVTBkcGtOaVI0R1cyNVo0ZXFLV0NuSWR5U2lJNndfWjJfYjloVGtNNU5KdTRsWFRJd2RaUUVwUzFmb0xhdkU4Y1NhbXdSd2ZxTmJuY2hMWC1Ub2k5U3ZwYlpvdlVWLXFWeHR6QjRKMXFYSg?oc=5</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Gunnison Country Times</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr"/>
@@ -13992,7 +13446,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>flood</t>
+          <t>wildfire</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -14003,12 +13457,12 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>815071602ea7a305ed23b696</t>
+          <t>f36621694d50360b5a1091ee</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>b52b9dfcd55a0b7eb55b1761</t>
+          <t>67c3e7e284a83a649e23c686</t>
         </is>
       </c>
       <c r="AE9" s="2" t="inlineStr"/>
@@ -14040,7 +13494,7 @@
       <c r="BA9" s="2" t="inlineStr"/>
       <c r="BB9" s="2" t="inlineStr">
         <is>
-          <t>ORLY</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="BC9" s="2" t="inlineStr">
@@ -14050,360 +13504,20 @@
       </c>
       <c r="BD9" s="2" t="inlineStr">
         <is>
-          <t>ORLY</t>
-        </is>
-      </c>
-      <c r="BE9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
+          <t>FAST</t>
+        </is>
+      </c>
+      <c r="BE9" s="2" t="inlineStr"/>
+      <c r="BF9" s="2" t="inlineStr"/>
       <c r="BG9" s="2" t="inlineStr"/>
       <c r="BH9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Fastenal</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Fast-moving wildfires leave forests less able to recover, Western study finds</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>'-0.849</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNSHVNc042bjFPcmNacmpBRDhJZUVMaEk2clhXSnk5U1pvWTMwN0pqN1hxbkdsMEhHc09LMEdVRlhwMkdmUDlOTXZZYUU3SzlfSTRsVTBkcGtOaVI0R1cyNVo0ZXFLV0NuSWR5U2lJNndfWjJfYjloVGtNNU5KdTRsWFRJd2RaUUVwUzFmb0xhdkU4Y1NhbXdSd2ZxTmJuY2hMWC1Ub2k5U3ZwYlpvdlVWLXFWeHR6QjRKMXFYSg?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Gunnison Country Times</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr"/>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>f36621694d50360b5a1091ee</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>67c3e7e284a83a649e23c686</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr"/>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BE10" s="2" t="inlineStr"/>
-      <c r="BF10" s="2" t="inlineStr"/>
-      <c r="BG10" s="2" t="inlineStr"/>
-      <c r="BH10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Delta Air Lines</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T05:13:58+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>美國聯邦貿易委員會（FTC）正考慮要求披露個性化定價</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>監管調查</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr"/>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NYSE-DAL/news/</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>FTC</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>5a8dc1a140bbb656bc23cba9</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>22a56251dfb3f01a27778045</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr"/>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr">
-        <is>
-          <t>DAL</t>
-        </is>
-      </c>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="4" t="inlineStr"/>
-      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH11"/>
+  <autoFilter ref="A1:BL9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14414,7 +13528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14477,6 +13591,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14780,9 +13898,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14793,7 +13931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14843,134 +13981,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -14980,46 +14118,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -15028,12 +14200,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -15043,90 +14215,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -15136,94 +14312,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -15231,89 +14407,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-20.xlsx
+++ b/news_daily/2026-08-20.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -1062,32 +1062,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1140,7 +1140,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>d85c41e3cc584e719bea14f4043905c7</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>13b919f6499b102da762eade</t>
@@ -1163,7 +1167,7 @@
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" s="2" t="inlineStr"/>
@@ -1205,10 +1209,22 @@
       </c>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1240,32 +1256,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1305,7 +1321,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1318,7 +1334,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>d84aa58faf654ac6a8d7d1c726865b4d</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>6b6667dfea00d2582f92d3ba</t>
@@ -1341,7 +1361,7 @@
       <c r="AN4" s="2" t="inlineStr"/>
       <c r="AO4" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP4" s="2" t="inlineStr"/>
@@ -1375,10 +1395,22 @@
       <c r="BF4" s="2" t="inlineStr"/>
       <c r="BG4" s="2" t="inlineStr"/>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1588,32 +1620,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1653,7 +1685,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1666,7 +1698,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>db72acdf0f3649f2acd81ad686e11778</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>5856b4783cb46f4b6d26b806</t>
@@ -1689,7 +1725,7 @@
       <c r="AN6" s="2" t="inlineStr"/>
       <c r="AO6" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP6" s="2" t="inlineStr"/>
@@ -1731,10 +1767,22 @@
       </c>
       <c r="BG6" s="2" t="inlineStr"/>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1963,13 +2011,17 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -2022,7 +2074,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB8" s="3" t="inlineStr"/>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>b2df647bd2d14a30be01e63f4f4c046e</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
           <t>bffacd740ad4708425d55112</t>
@@ -2043,7 +2099,11 @@
       <c r="AL8" s="3" t="inlineStr"/>
       <c r="AM8" s="3" t="inlineStr"/>
       <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="3" t="inlineStr"/>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr"/>
@@ -2081,364 +2141,420 @@
       <c r="BH8" s="3" t="inlineStr"/>
       <c r="BI8" s="3" t="inlineStr"/>
       <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="BK8" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>DOW</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Dow Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Dow drops 600 points on rising yields, Walmart earnings miss</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>'-0.867</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPdkZjeVRodzA3MTZYMHotdkdIUGVudDdROUs4aDNCNW53cDVWNzNhczZwanNrNUswMUZLaG9CNXZxMzJsNV90Z1duTy0tdUU1RUt2aEpkMGxPRVo5dEk3UFlLQ2Y2dnQtTnJxTmZ2ZVpLbTVQaHZMZ1oyWmF3RzlUOUp0cXYzY1dOV3FOYkZ1SURCMU5scEI1MjZ3?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>earnings miss</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>cffd1a9c85434f6080d0b6296b342bf9</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>93dff53ed6252c05773bcbb2</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr">
+        <is>
+          <t>cd9e7fa383a3406940cf5220</t>
+        </is>
+      </c>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>'-0.867</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPdkZjeVRodzA3MTZYMHotdkdIUGVudDdROUs4aDNCNW53cDVWNzNhczZwanNrNUswMUZLaG9CNXZxMzJsNV90Z1duTy0tdUU1RUt2aEpkMGxPRVo5dEk3UFlLQ2Y2dnQtTnJxTmZ2ZVpLbTVQaHZMZ1oyWmF3RzlUOUp0cXYzY1dOV3FOYkZ1SURCMU5scEI1MjZ3?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>earnings miss</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>93dff53ed6252c05773bcbb2</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>cd9e7fa383a3406940cf5220</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr">
+      <c r="AP9" s="2" t="inlineStr"/>
+      <c r="AQ9" s="2" t="inlineStr"/>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr"/>
+      <c r="AT9" s="2" t="inlineStr"/>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
+      <c r="AX9" s="2" t="inlineStr"/>
+      <c r="AY9" s="2" t="inlineStr"/>
+      <c r="AZ9" s="2" t="inlineStr"/>
+      <c r="BA9" s="2" t="inlineStr"/>
+      <c r="BB9" s="2" t="inlineStr">
         <is>
           <t>DOW</t>
         </is>
       </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="BC9" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="2" t="inlineStr"/>
+      <c r="BE9" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr">
+      <c r="BF9" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BG9" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>AZO</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>AutoZone, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Advance Auto Parts Plunges 21% as Revenue Miss Overshadows Earnings Beat; AutoZone Falls 4%, O'Reilly Automotive Slips</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>財報不如預期</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>'-0.948</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOd1p2bjkybHktQ2RmSlM5dUp3dmNiNFpZZ0JoWEt2VjY3Vi1LWUhkSmlxNkttdFRDMkZ4SUkxSnltZXh6MjdtTy1HalZ3R3lHcFU1X2tNUGp4cFAzV0Y2TC1VTzFqanNIVkJOQjJCSXZMb2k5bWwwcnIxcHBYSmdWdkVtcWU5aUVaZUg0dUxBcnl1czRMd3JXSVBBejVvUjRIOU92MG9XQTd4Vk1vNkNhNGlzbkdrWVk5ZlhzLUlEcWRFSnNrQVNzNkh0ak9kdnBxM0ZIMGJXOEh4TnlwNmlucjdPRGg5ZFcya3VSVHp3?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>24/7 Wall St.</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>FINANCIAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>revenue miss</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>4409ac5e7cac451cbe4ad28e4314b8b8</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>8c38c6059b8ffe5c1de6ef60</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>908d5cfc2f0f8f14818d4cd3</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>'-0.948</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOd1p2bjkybHktQ2RmSlM5dUp3dmNiNFpZZ0JoWEt2VjY3Vi1LWUhkSmlxNkttdFRDMkZ4SUkxSnltZXh6MjdtTy1HalZ3R3lHcFU1X2tNUGp4cFAzV0Y2TC1VTzFqanNIVkJOQjJCSXZMb2k5bWwwcnIxcHBYSmdWdkVtcWU5aUVaZUg0dUxBcnl1czRMd3JXSVBBejVvUjRIOU92MG9XQTd4Vk1vNkNhNGlzbkdrWVk5ZlhzLUlEcWRFSnNrQVNzNkh0ak9kdnBxM0ZIMGJXOEh4TnlwNmlucjdPRGg5ZFcya3VSVHp3?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>24/7 Wall St.</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>EARNINGS_MISS</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>revenue miss</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>8c38c6059b8ffe5c1de6ef60</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>908d5cfc2f0f8f14818d4cd3</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
         <is>
           <t>AZO</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="3" t="inlineStr"/>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr"/>
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr">
+      <c r="BG10" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -2479,7 +2595,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>營運惡化</t>
+          <t>財測下修</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2489,13 +2605,17 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -2535,7 +2655,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>OPERATING_DETERIORATION</t>
+          <t>EARNINGS_WARNING</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -2548,7 +2668,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>9f1a76d20bda48fa99fb838579efc7a9</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
           <t>9557c75c7fa4f2cc72385ef6</t>
@@ -2569,7 +2693,11 @@
       <c r="AL11" s="3" t="inlineStr"/>
       <c r="AM11" s="3" t="inlineStr"/>
       <c r="AN11" s="3" t="inlineStr"/>
-      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="3" t="inlineStr"/>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
@@ -2613,10 +2741,22 @@
         </is>
       </c>
       <c r="BH11" s="3" t="inlineStr"/>
-      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="3" t="inlineStr"/>
-      <c r="BK11" s="3" t="inlineStr"/>
-      <c r="BL11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2667,13 +2807,17 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2726,7 +2870,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>6e832f36f2f445a8af8f5b98ec5180f3</t>
+        </is>
+      </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
           <t>3de52fe7865a8ab9d3c5f24d</t>
@@ -2747,7 +2895,11 @@
       <c r="AL12" s="3" t="inlineStr"/>
       <c r="AM12" s="3" t="inlineStr"/>
       <c r="AN12" s="3" t="inlineStr"/>
-      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="3" t="inlineStr"/>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr"/>
@@ -2793,526 +2945,598 @@
       <c r="BH12" s="3" t="inlineStr"/>
       <c r="BI12" s="3" t="inlineStr"/>
       <c r="BJ12" s="3" t="inlineStr"/>
-      <c r="BK12" s="3" t="inlineStr"/>
-      <c r="BL12" s="3" t="inlineStr"/>
+      <c r="BK12" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Bunge Global</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>How Revenue Growth Amid Margin Pressure Will Impact Bunge Global (BG) Investors</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>'-0.239</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT1gyMkpjS3NWOExpbHVpV0pybzU1ZHp3d1JUVUd3M3JPWDh3YW03MmtnYWdQZjNJcDBCZVI2VzlZMzBCc3BqMmpFNWVDZllSYVNsNXp3a0FDaUw0ekh5YVNiSVI0R2lYa3dlQ0pKaUJ5SnRuZHBDbVBHa0JwbUwta2JlRFltd1l2VURzWFdFYTFzZWd4czBReE1oZ2dOc096eERkc1JncGJEejdTZGtScmNKRDJmdkt3dTUwLXpiTzM2ZnZQSG1DUU9oOTY1akZqSllJYno5c9IB3AFBVV95cUxQVUR3UFozVVRCQUJnRVI3M24tQmVPclJKQUZzdGM0OFNES2tKc0U2NmxjMHVjVkN2MVdXcVRoWjRGdVFUUHZVbW81dHN1RzdoSWlDMWFCNFNoNDRTX2swc0xEa1FBMEFrcVpJYUR5by02QnhzNkNuN1Bfd3JkSUhSTjh3NldtZkJUcFA2dktPZmQ1SXJBSGw4SEh2M203ajFPdDNMVUVTTW1vNWRXXzcxVFJIcUl0YU9kRFpYR2FmZEM2bWhIRWtVMWMwM25QT0pxenZyUUczSHN1TnN1?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>margin pressure</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>d6043ce0571c49d2809f40de9ddb1fc1</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>57d1f643bbd8d6fdb0f93bb9</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr">
+        <is>
+          <t>ee61869adc7dc1e65e326d0e</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>'-0.239</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT1gyMkpjS3NWOExpbHVpV0pybzU1ZHp3d1JUVUd3M3JPWDh3YW03MmtnYWdQZjNJcDBCZVI2VzlZMzBCc3BqMmpFNWVDZllSYVNsNXp3a0FDaUw0ekh5YVNiSVI0R2lYa3dlQ0pKaUJ5SnRuZHBDbVBHa0JwbUwta2JlRFltd1l2VURzWFdFYTFzZWd4czBReE1oZ2dOc096eERkc1JncGJEejdTZGtScmNKRDJmdkt3dTUwLXpiTzM2ZnZQSG1DUU9oOTY1akZqSllJYno5c9IB3AFBVV95cUxQVUR3UFozVVRCQUJnRVI3M24tQmVPclJKQUZzdGM0OFNES2tKc0U2NmxjMHVjVkN2MVdXcVRoWjRGdVFUUHZVbW81dHN1RzdoSWlDMWFCNFNoNDRTX2swc0xEa1FBMEFrcVpJYUR5by02QnhzNkNuN1Bfd3JkSUhSTjh3NldtZkJUcFA2dktPZmQ1SXJBSGw4SEh2M203ajFPdDNMVUVTTW1vNWRXXzcxVFJIcUl0YU9kRFpYR2FmZEM2bWhIRWtVMWMwM25QT0pxenZyUUczSHN1TnN1?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA13" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="3" t="inlineStr">
-        <is>
-          <t>57d1f643bbd8d6fdb0f93bb9</t>
-        </is>
-      </c>
-      <c r="AD13" s="3" t="inlineStr">
-        <is>
-          <t>ee61869adc7dc1e65e326d0e</t>
-        </is>
-      </c>
-      <c r="AE13" s="3" t="inlineStr"/>
-      <c r="AF13" s="3" t="inlineStr"/>
-      <c r="AG13" s="3" t="inlineStr"/>
-      <c r="AH13" s="3" t="inlineStr"/>
-      <c r="AI13" s="3" t="inlineStr"/>
-      <c r="AJ13" s="3" t="inlineStr"/>
-      <c r="AK13" s="3" t="inlineStr"/>
-      <c r="AL13" s="3" t="inlineStr"/>
-      <c r="AM13" s="3" t="inlineStr"/>
-      <c r="AN13" s="3" t="inlineStr"/>
-      <c r="AO13" s="3" t="inlineStr"/>
-      <c r="AP13" s="3" t="inlineStr"/>
-      <c r="AQ13" s="3" t="inlineStr"/>
-      <c r="AR13" s="3" t="inlineStr"/>
-      <c r="AS13" s="3" t="inlineStr"/>
-      <c r="AT13" s="3" t="inlineStr"/>
-      <c r="AU13" s="3" t="inlineStr"/>
-      <c r="AV13" s="3" t="inlineStr"/>
-      <c r="AW13" s="3" t="inlineStr"/>
-      <c r="AX13" s="3" t="inlineStr"/>
-      <c r="AY13" s="3" t="inlineStr"/>
-      <c r="AZ13" s="3" t="inlineStr"/>
-      <c r="BA13" s="3" t="inlineStr"/>
-      <c r="BB13" s="3" t="inlineStr">
+      <c r="AP13" s="2" t="inlineStr"/>
+      <c r="AQ13" s="2" t="inlineStr"/>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr"/>
+      <c r="AT13" s="2" t="inlineStr"/>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr"/>
+      <c r="AX13" s="2" t="inlineStr"/>
+      <c r="AY13" s="2" t="inlineStr"/>
+      <c r="AZ13" s="2" t="inlineStr"/>
+      <c r="BA13" s="2" t="inlineStr"/>
+      <c r="BB13" s="2" t="inlineStr">
         <is>
           <t>BG</t>
         </is>
       </c>
-      <c r="BC13" s="3" t="inlineStr">
+      <c r="BC13" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD13" s="3" t="inlineStr"/>
-      <c r="BE13" s="3" t="inlineStr">
+      <c r="BD13" s="2" t="inlineStr"/>
+      <c r="BE13" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF13" s="3" t="inlineStr"/>
-      <c r="BG13" s="3" t="inlineStr">
+      <c r="BF13" s="2" t="inlineStr"/>
+      <c r="BG13" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH13" s="3" t="inlineStr"/>
-      <c r="BI13" s="3" t="inlineStr"/>
-      <c r="BJ13" s="3" t="inlineStr"/>
-      <c r="BK13" s="3" t="inlineStr"/>
-      <c r="BL13" s="3" t="inlineStr"/>
+      <c r="BH13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>KeyCorp</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SB Nation Reacts Poll Results: Is Run Differential a Playoff Success Key</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUERxYXpCOHJWOHlpQW4yUDg5dkdSS3VHTzNSeDVDN0ltQjJDRlpOTFJ3dkdJa2pSV0JQSW1MX2llejY3Uy1DRVBqOW5xQ0hncFQySklZU2FFdTcyNklTLUdrTEpuS050U0tENW5JVHdBU2JtcVN6MWdKYXdGeDg1RTBTajFMdnY2Z1gtTEdoZUtRamtRZmo3bk9jTWFFbnVmdmxweHJvX3BmS25HU0VVb2M3MktqN1dWM0YwSThGYi1SLThhMTJ3UnhEYUJfUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>crawfishboxes.com</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>3f4d5bb135804a44bce819fa8c1eb880</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>827e29b8562554996132c201</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t>e15452dd3993cf8b4f47594b</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="AP14" s="2" t="inlineStr"/>
+      <c r="AQ14" s="2" t="inlineStr"/>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr"/>
+      <c r="AT14" s="2" t="inlineStr"/>
+      <c r="AU14" s="2" t="inlineStr"/>
+      <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" s="2" t="inlineStr"/>
+      <c r="AX14" s="2" t="inlineStr"/>
+      <c r="AY14" s="2" t="inlineStr"/>
+      <c r="AZ14" s="2" t="inlineStr"/>
+      <c r="BA14" s="2" t="inlineStr"/>
+      <c r="BB14" s="2" t="inlineStr">
+        <is>
+          <t>KEY</t>
+        </is>
+      </c>
+      <c r="BC14" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUERxYXpCOHJWOHlpQW4yUDg5dkdSS3VHTzNSeDVDN0ltQjJDRlpOTFJ3dkdJa2pSV0JQSW1MX2llejY3Uy1DRVBqOW5xQ0hncFQySklZU2FFdTcyNklTLUdrTEpuS050U0tENW5JVHdBU2JtcVN6MWdKYXdGeDg1RTBTajFMdnY2Z1gtTEdoZUtRamtRZmo3bk9jTWFFbnVmdmxweHJvX3BmS25HU0VVb2M3MktqN1dWM0YwSThGYi1SLThhMTJ3UnhEYUJfUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t>crawfishboxes.com</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA14" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="3" t="inlineStr">
-        <is>
-          <t>827e29b8562554996132c201</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>e15452dd3993cf8b4f47594b</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="inlineStr"/>
-      <c r="AF14" s="3" t="inlineStr"/>
-      <c r="AG14" s="3" t="inlineStr"/>
-      <c r="AH14" s="3" t="inlineStr"/>
-      <c r="AI14" s="3" t="inlineStr"/>
-      <c r="AJ14" s="3" t="inlineStr"/>
-      <c r="AK14" s="3" t="inlineStr"/>
-      <c r="AL14" s="3" t="inlineStr"/>
-      <c r="AM14" s="3" t="inlineStr"/>
-      <c r="AN14" s="3" t="inlineStr"/>
-      <c r="AO14" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
-      <c r="AR14" s="3" t="inlineStr"/>
-      <c r="AS14" s="3" t="inlineStr"/>
-      <c r="AT14" s="3" t="inlineStr"/>
-      <c r="AU14" s="3" t="inlineStr"/>
-      <c r="AV14" s="3" t="inlineStr"/>
-      <c r="AW14" s="3" t="inlineStr"/>
-      <c r="AX14" s="3" t="inlineStr"/>
-      <c r="AY14" s="3" t="inlineStr"/>
-      <c r="AZ14" s="3" t="inlineStr"/>
-      <c r="BA14" s="3" t="inlineStr"/>
-      <c r="BB14" s="3" t="inlineStr">
+      <c r="BD14" s="2" t="inlineStr">
         <is>
           <t>KEY</t>
         </is>
       </c>
-      <c r="BC14" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD14" s="3" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BE14" s="3" t="inlineStr">
+      <c r="BE14" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF14" s="3" t="inlineStr">
+      <c r="BF14" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG14" s="3" t="inlineStr"/>
-      <c r="BH14" s="3" t="inlineStr"/>
-      <c r="BI14" s="3" t="inlineStr"/>
-      <c r="BJ14" s="3" t="inlineStr"/>
-      <c r="BK14" s="3" t="inlineStr"/>
-      <c r="BL14" s="3" t="inlineStr"/>
+      <c r="BG14" s="2" t="inlineStr"/>
+      <c r="BH14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>BBY</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Best Buy</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Best Buy achieves zero waste goal at supply chain facilities</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>0.665</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQd3pOOHJGWjJZdXhzWXJxQjExdWYwU3dwR1RlbzEyWEgzT3JDUmNxWFIyMVNJa2tWaDYzdWxqZ1JHRnFRU1pERnR6Y05wdGlkUjM2NEpSekVHVmM2Sy1HYU9vMTV3NW9reUVxYi15eENsYVE1OVJJMWZLb2FPZlRORHo1RjB3eTFyWDJiWktHZ29peldLS29vdUt1clJjQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>esgdive.com</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>51a5ec65362f4c50b1a6d81916e5be05</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>85d1addc8a08864dc793f988</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t>9b91acd3984657a709b46053</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="2" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>0.665</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQd3pOOHJGWjJZdXhzWXJxQjExdWYwU3dwR1RlbzEyWEgzT3JDUmNxWFIyMVNJa2tWaDYzdWxqZ1JHRnFRU1pERnR6Y05wdGlkUjM2NEpSekVHVmM2Sy1HYU9vMTV3NW9reUVxYi15eENsYVE1OVJJMWZLb2FPZlRORHo1RjB3eTFyWDJiWktHZ29peldLS29vdUt1clJjQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>esgdive.com</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>85d1addc8a08864dc793f988</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>9b91acd3984657a709b46053</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr"/>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
+      <c r="AP15" s="2" t="inlineStr"/>
+      <c r="AQ15" s="2" t="inlineStr"/>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr"/>
+      <c r="AT15" s="2" t="inlineStr"/>
+      <c r="AU15" s="2" t="inlineStr"/>
+      <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" s="2" t="inlineStr"/>
+      <c r="AX15" s="2" t="inlineStr"/>
+      <c r="AY15" s="2" t="inlineStr"/>
+      <c r="AZ15" s="2" t="inlineStr"/>
+      <c r="BA15" s="2" t="inlineStr"/>
+      <c r="BB15" s="2" t="inlineStr">
         <is>
           <t>BBY</t>
         </is>
       </c>
-      <c r="BC15" s="3" t="inlineStr">
+      <c r="BC15" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
+      <c r="BD15" s="2" t="inlineStr"/>
+      <c r="BE15" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF15" s="3" t="inlineStr"/>
-      <c r="BG15" s="3" t="inlineStr">
+      <c r="BF15" s="2" t="inlineStr"/>
+      <c r="BG15" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
+      <c r="BH15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3557,13 +3781,17 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -3616,7 +3844,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>0673fc30b3e54fc5b8d29e382dbd059b</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
           <t>321791372228eac0ca214be6</t>
@@ -3637,7 +3869,11 @@
       <c r="AL17" s="3" t="inlineStr"/>
       <c r="AM17" s="3" t="inlineStr"/>
       <c r="AN17" s="3" t="inlineStr"/>
-      <c r="AO17" s="3" t="inlineStr"/>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="3" t="inlineStr"/>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr"/>
@@ -3683,8 +3919,16 @@
       <c r="BH17" s="3" t="inlineStr"/>
       <c r="BI17" s="3" t="inlineStr"/>
       <c r="BJ17" s="3" t="inlineStr"/>
-      <c r="BK17" s="3" t="inlineStr"/>
-      <c r="BL17" s="3" t="inlineStr"/>
+      <c r="BK17" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -5485,13 +5729,17 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -5544,7 +5792,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB27" s="3" t="inlineStr"/>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>ee2b459ce4f145699a422057ec325b55</t>
+        </is>
+      </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
           <t>197a030e866462b53c92be76</t>
@@ -5565,7 +5817,11 @@
       <c r="AL27" s="3" t="inlineStr"/>
       <c r="AM27" s="3" t="inlineStr"/>
       <c r="AN27" s="3" t="inlineStr"/>
-      <c r="AO27" s="3" t="inlineStr"/>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP27" s="3" t="inlineStr"/>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr"/>
@@ -5611,8 +5867,16 @@
       <c r="BH27" s="3" t="inlineStr"/>
       <c r="BI27" s="3" t="inlineStr"/>
       <c r="BJ27" s="3" t="inlineStr"/>
-      <c r="BK27" s="3" t="inlineStr"/>
-      <c r="BL27" s="3" t="inlineStr"/>
+      <c r="BK27" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5992,32 +6256,32 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6057,7 +6321,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -6070,7 +6334,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>e9a07cc75d1b43daba2fb42e838bf8f3</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>710d96aeafcd9dd89a0947b6</t>
@@ -6093,7 +6361,7 @@
       <c r="AN30" s="2" t="inlineStr"/>
       <c r="AO30" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP30" s="2" t="inlineStr"/>
@@ -6127,10 +6395,22 @@
       <c r="BF30" s="2" t="inlineStr"/>
       <c r="BG30" s="2" t="inlineStr"/>
       <c r="BH30" s="2" t="inlineStr"/>
-      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6162,32 +6442,32 @@
       <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -6227,7 +6507,7 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -6240,7 +6520,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>8e000ec422f144b7aec80830ff03da31</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
           <t>ba8d55b8d4bcb962a9c92d34</t>
@@ -6263,7 +6547,7 @@
       <c r="AN31" s="2" t="inlineStr"/>
       <c r="AO31" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP31" s="2" t="inlineStr"/>
@@ -6297,10 +6581,22 @@
       <c r="BF31" s="2" t="inlineStr"/>
       <c r="BG31" s="2" t="inlineStr"/>
       <c r="BH31" s="2" t="inlineStr"/>
-      <c r="BI31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ31" s="2" t="inlineStr"/>
-      <c r="BK31" s="2" t="inlineStr"/>
-      <c r="BL31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6688,32 +6984,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6753,7 +7049,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6766,7 +7062,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>dfd79f01a2b54b8fa1d82c5cb06da2ed</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>815071602ea7a305ed23b696</t>
@@ -6789,7 +7089,7 @@
       <c r="AN34" s="2" t="inlineStr"/>
       <c r="AO34" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP34" s="2" t="inlineStr"/>
@@ -6831,10 +7131,22 @@
       </c>
       <c r="BG34" s="2" t="inlineStr"/>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7894,32 +8206,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -7959,7 +8271,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -7972,7 +8284,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>e47bae1995a1496aa6e95662e5713651</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>f36621694d50360b5a1091ee</t>
@@ -7995,7 +8311,7 @@
       <c r="AN41" s="2" t="inlineStr"/>
       <c r="AO41" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP41" s="2" t="inlineStr"/>
@@ -8029,10 +8345,22 @@
       <c r="BF41" s="2" t="inlineStr"/>
       <c r="BG41" s="2" t="inlineStr"/>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8427,182 +8755,206 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>International Business Machines Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>2026-08-20T04:01:00+08:00</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>IBM’s 2026 Data Breach Report: Houston, We Have A Problem</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>'-0.946</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUXZUWlJkaXVxNldYVjRSMXowQ0xFTWw2SXcwdVppbUFsR05qWVFIejc3eXNoMkRSWnVxaVdtS0RjcC1DVVZtN0FxLTJMNHlzMEdpS3IxSUhUMW5DcmMxbW5SUkl6VF8wZnFaM2Ytd1gzR3AzNE1CR3J3djQxNlE5Y2M0X0N0Z0xJN21ZTEtYYXU?oc=5</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Above the Law</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>e7e3df4a1df240c09a0e0771c2f3f9a7</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>2ff2c3663d180b21905740d5</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>b5fb7ce9cc34eee18630b78a</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+      <c r="AK44" s="2" t="inlineStr"/>
+      <c r="AL44" s="2" t="inlineStr"/>
+      <c r="AM44" s="2" t="inlineStr"/>
+      <c r="AN44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>'-0.946</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
-      <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUXZUWlJkaXVxNldYVjRSMXowQ0xFTWw2SXcwdVppbUFsR05qWVFIejc3eXNoMkRSWnVxaVdtS0RjcC1DVVZtN0FxLTJMNHlzMEdpS3IxSUhUMW5DcmMxbW5SUkl6VF8wZnFaM2Ytd1gzR3AzNE1CR3J3djQxNlE5Y2M0X0N0Z0xJN21ZTEtYYXU?oc=5</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t>Above the Law</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB44" s="3" t="inlineStr"/>
-      <c r="AC44" s="3" t="inlineStr">
-        <is>
-          <t>2ff2c3663d180b21905740d5</t>
-        </is>
-      </c>
-      <c r="AD44" s="3" t="inlineStr">
-        <is>
-          <t>b5fb7ce9cc34eee18630b78a</t>
-        </is>
-      </c>
-      <c r="AE44" s="3" t="inlineStr"/>
-      <c r="AF44" s="3" t="inlineStr"/>
-      <c r="AG44" s="3" t="inlineStr"/>
-      <c r="AH44" s="3" t="inlineStr"/>
-      <c r="AI44" s="3" t="inlineStr"/>
-      <c r="AJ44" s="3" t="inlineStr"/>
-      <c r="AK44" s="3" t="inlineStr"/>
-      <c r="AL44" s="3" t="inlineStr"/>
-      <c r="AM44" s="3" t="inlineStr"/>
-      <c r="AN44" s="3" t="inlineStr"/>
-      <c r="AO44" s="3" t="inlineStr"/>
-      <c r="AP44" s="3" t="inlineStr"/>
-      <c r="AQ44" s="3" t="inlineStr"/>
-      <c r="AR44" s="3" t="inlineStr"/>
-      <c r="AS44" s="3" t="inlineStr"/>
-      <c r="AT44" s="3" t="inlineStr"/>
-      <c r="AU44" s="3" t="inlineStr"/>
-      <c r="AV44" s="3" t="inlineStr"/>
-      <c r="AW44" s="3" t="inlineStr">
+      <c r="AP44" s="2" t="inlineStr"/>
+      <c r="AQ44" s="2" t="inlineStr"/>
+      <c r="AR44" s="2" t="inlineStr"/>
+      <c r="AS44" s="2" t="inlineStr"/>
+      <c r="AT44" s="2" t="inlineStr"/>
+      <c r="AU44" s="2" t="inlineStr"/>
+      <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX44" s="3" t="inlineStr"/>
-      <c r="AY44" s="3" t="inlineStr"/>
-      <c r="AZ44" s="3" t="inlineStr"/>
-      <c r="BA44" s="3" t="inlineStr"/>
-      <c r="BB44" s="3" t="inlineStr">
+      <c r="AX44" s="2" t="inlineStr"/>
+      <c r="AY44" s="2" t="inlineStr"/>
+      <c r="AZ44" s="2" t="inlineStr"/>
+      <c r="BA44" s="2" t="inlineStr"/>
+      <c r="BB44" s="2" t="inlineStr">
         <is>
           <t>IBM</t>
         </is>
       </c>
-      <c r="BC44" s="3" t="inlineStr">
+      <c r="BC44" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD44" s="3" t="inlineStr"/>
-      <c r="BE44" s="3" t="inlineStr">
+      <c r="BD44" s="2" t="inlineStr"/>
+      <c r="BE44" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF44" s="3" t="inlineStr">
+      <c r="BF44" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG44" s="3" t="inlineStr">
+      <c r="BG44" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH44" s="3" t="inlineStr"/>
-      <c r="BI44" s="3" t="inlineStr"/>
-      <c r="BJ44" s="3" t="inlineStr"/>
-      <c r="BK44" s="3" t="inlineStr"/>
-      <c r="BL44" s="3" t="inlineStr"/>
+      <c r="BH44" s="2" t="inlineStr"/>
+      <c r="BI44" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ44" s="2" t="inlineStr"/>
+      <c r="BK44" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL44"/>
@@ -8616,7 +8968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL16"/>
+  <dimension ref="A1:BL10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9056,13 +9408,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -9115,7 +9471,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>b2df647bd2d14a30be01e63f4f4c046e</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>bffacd740ad4708425d55112</t>
@@ -9136,7 +9496,11 @@
       <c r="AL2" s="3" t="inlineStr"/>
       <c r="AM2" s="3" t="inlineStr"/>
       <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr"/>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="3" t="inlineStr"/>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr"/>
@@ -9174,8 +9538,16 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -9190,12 +9562,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dow Inc. Common Stock </t>
+          <t>Fiserv, Inc.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -9205,7 +9577,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Dow drops 600 points on rising yields, Walmart earnings miss</t>
+          <t>Fiserv's 2026 Outlook Cut Puts Revenue and Margin Pressure in Focus</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr"/>
@@ -9216,7 +9588,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>財測下修</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -9226,13 +9598,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -9242,7 +9618,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>'-0.867</t>
+          <t>'-0.95</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
@@ -9256,7 +9632,7 @@
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxPdkZjeVRodzA3MTZYMHotdkdIUGVudDdROUs4aDNCNW53cDVWNzNhczZwanNrNUswMUZLaG9CNXZxMzJsNV90Z1duTy0tdUU1RUt2aEpkMGxPRVo5dEk3UFlLQ2Y2dnQtTnJxTmZ2ZVpLbTVQaHZMZ1oyWmF3RzlUOUp0cXYzY1dOV3FOYkZ1SURCMU5scEI1MjZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOTFY0dkxpbHZIc3NjWUFqUDRNLTVNbkJydlU2OGNmcW53TlNRelVwZGZIQlE2Q0ZwZVAyZTgyT1RRbmVkd1d5UFpmZVg5c29MNlVaeVRNRW51aHRqUC02WTdpTFptWWJSQ3VPRU9pNWVsOGRhT1pfbU1SMU9EeDdEU3ZHWGlJQ0dCUmFNMk02aEotQXVpVlphYnBR?oc=5</t>
         </is>
       </c>
       <c r="V3" s="3" t="inlineStr">
@@ -9267,17 +9643,17 @@
       <c r="W3" s="3" t="inlineStr"/>
       <c r="X3" s="3" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>EARNINGS_WARNING</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
-          <t>earnings miss</t>
+          <t>margin pressure</t>
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr">
@@ -9285,15 +9661,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>9f1a76d20bda48fa99fb838579efc7a9</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>93dff53ed6252c05773bcbb2</t>
+          <t>9557c75c7fa4f2cc72385ef6</t>
         </is>
       </c>
       <c r="AD3" s="3" t="inlineStr">
         <is>
-          <t>cd9e7fa383a3406940cf5220</t>
+          <t>b85fb47a39549e96690d81d4</t>
         </is>
       </c>
       <c r="AE3" s="3" t="inlineStr"/>
@@ -9306,7 +9686,11 @@
       <c r="AL3" s="3" t="inlineStr"/>
       <c r="AM3" s="3" t="inlineStr"/>
       <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="3" t="inlineStr"/>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr"/>
@@ -9316,7 +9700,7 @@
       <c r="AV3" s="3" t="inlineStr"/>
       <c r="AW3" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX3" s="3" t="inlineStr"/>
@@ -9325,7 +9709,7 @@
       <c r="BA3" s="3" t="inlineStr"/>
       <c r="BB3" s="3" t="inlineStr">
         <is>
-          <t>DOW</t>
+          <t>FISV</t>
         </is>
       </c>
       <c r="BC3" s="3" t="inlineStr">
@@ -9336,12 +9720,12 @@
       <c r="BD3" s="3" t="inlineStr"/>
       <c r="BE3" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG3" s="3" t="inlineStr">
@@ -9350,10 +9734,22 @@
         </is>
       </c>
       <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -9368,12 +9764,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>AutoZone, Inc. Common Stock</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -9383,7 +9779,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Advance Auto Parts Plunges 21% as Revenue Miss Overshadows Earnings Beat; AutoZone Falls 4%, O'Reilly Automotive Slips</t>
+          <t>Starbucks files another layoff notice for Seattle HQ, 200+ jobs affected</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
@@ -9394,7 +9790,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>財報不如預期</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -9404,13 +9800,17 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -9420,7 +9820,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>'-0.948</t>
+          <t>'-0.956</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
@@ -9434,28 +9834,28 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOd1p2bjkybHktQ2RmSlM5dUp3dmNiNFpZZ0JoWEt2VjY3Vi1LWUhkSmlxNkttdFRDMkZ4SUkxSnltZXh6MjdtTy1HalZ3R3lHcFU1X2tNUGp4cFAzV0Y2TC1VTzFqanNIVkJOQjJCSXZMb2k5bWwwcnIxcHBYSmdWdkVtcWU5aUVaZUg0dUxBcnl1czRMd3JXSVBBejVvUjRIOU92MG9XQTd4Vk1vNkNhNGlzbkdrWVk5ZlhzLUlEcWRFSnNrQVNzNkh0ak9kdnBxM0ZIMGJXOEh4TnlwNmlucjdPRGg5ZFcya3VSVHp3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxQWlRnaTdmazJ4N3IwcUtpSTFpZ2x0aEowUlhWWlBFRC1XVWxjWFktUUpXQmhxOTgweV9oSm02cUcxSmZGNmFlS1ltOWJoMHJvUjRfRUxhWGRXM2lCdTVYV1dTYTlFT1JsMWxGVUZfR0Z1VlNrMndzZnk4X2gzNTA1TXJVT2c4OHh4emZaZlhmbXZhbloyRV95U0pCbGxBQ0RER2tQUUxVOFdwdUExcDdLSlp6MEUzaWlxTjhhZzdUdEZ3R0YwUmJBenFVcTNVWm5rdDVRbFFyekFLYzV5aXM4VmpRLVprNnBROVB4cVZFUTVZelBFeXU0b3BsOU5VTlJXU0xDSkZGNHlIX0NyZm5pd1YxX21UMXhSRTR4bWp0ZE03LTVQdUZTbGU5aXgzM1NteTIyS3ZVcEE?oc=5</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t>24/7 Wall St.</t>
+          <t>KOMO</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr"/>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>FINANCIAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>EARNINGS_MISS</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>revenue miss</t>
+          <t>layoff</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -9463,15 +9863,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>6e832f36f2f445a8af8f5b98ec5180f3</t>
+        </is>
+      </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>8c38c6059b8ffe5c1de6ef60</t>
+          <t>3de52fe7865a8ab9d3c5f24d</t>
         </is>
       </c>
       <c r="AD4" s="3" t="inlineStr">
         <is>
-          <t>908d5cfc2f0f8f14818d4cd3</t>
+          <t>57fcfed4161a89c6cda80114</t>
         </is>
       </c>
       <c r="AE4" s="3" t="inlineStr"/>
@@ -9484,7 +9888,11 @@
       <c r="AL4" s="3" t="inlineStr"/>
       <c r="AM4" s="3" t="inlineStr"/>
       <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="3" t="inlineStr"/>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr"/>
@@ -9494,7 +9902,7 @@
       <c r="AV4" s="3" t="inlineStr"/>
       <c r="AW4" s="3" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="AX4" s="3" t="inlineStr"/>
@@ -9503,7 +9911,7 @@
       <c r="BA4" s="3" t="inlineStr"/>
       <c r="BB4" s="3" t="inlineStr">
         <is>
-          <t>AZO</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="BC4" s="3" t="inlineStr">
@@ -9514,12 +9922,12 @@
       <c r="BD4" s="3" t="inlineStr"/>
       <c r="BE4" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF4" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
       <c r="BG4" s="3" t="inlineStr">
@@ -9530,8 +9938,16 @@
       <c r="BH4" s="3" t="inlineStr"/>
       <c r="BI4" s="3" t="inlineStr"/>
       <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -9546,12 +9962,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Fiserv, Inc.</t>
+          <t>Starbucks Corporation</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -9561,7 +9977,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Fiserv's 2026 Outlook Cut Puts Revenue and Margin Pressure in Focus</t>
+          <t>Starbucks layoffs hit 224 Seattle headquarters employees</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr"/>
@@ -9572,7 +9988,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>營運惡化</t>
+          <t>裁員或人力縮減</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -9582,13 +9998,17 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -9598,7 +10018,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>'-0.95</t>
+          <t>'-0.959</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
@@ -9612,12 +10032,12 @@
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOTFY0dkxpbHZIc3NjWUFqUDRNLTVNbkJydlU2OGNmcW53TlNRelVwZGZIQlE2Q0ZwZVAyZTgyT1RRbmVkd1d5UFpmZVg5c29MNlVaeVRNRW51aHRqUC02WTdpTFptWWJSQ3VPRU9pNWVsOGRhT1pfbU1SMU9EeDdEU3ZHWGlJQ0dCUmFNMk02aEotQXVpVlphYnBR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNLXBaMkcyQTUzUnFPa0I4OWduRXRBUnFNTml3TXhfV3BpbVh5Y082bVRFdkFSWG01aF9aWVJGWXRHMFBrNl9Hdk96eDFzYkxqRTVSVEdPQWY4SHVEcGY4TTNTWHA0NWxtdUlHeDRfY25oR0JVX3FvMDVGQnl1LUpEQUNKajRFUktOWGp3WE1XLVhEbmpfOUlsS2FENUd3d0pocldhZ05mOEZUcjJfUVHSAbMBQVVfeXFMTjlxSHpUbFdwd2ZhWXVQMGFTZ0xQMjNoQWVJeTgzWXE5aVh6cFFTTzY0eDB1eDRaRW9YZmtfb2lKRGVqZl90TTg0ak93MEI3ZGhPRzFGa09Bbk9xTnlScURocmJ5TnVxNFN0c0VzelNDaFdtZzZSYzVxcy01eW9pTlF0VDdDLUdCWDl0S0hiMThZQ2JkT09fMDloUHN0bnpzTGJWM0F6RVRtdkdDYzd2eVNNeFU?oc=5</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t>finance.yahoo.com</t>
+          <t>FOX 13 Seattle</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr"/>
@@ -9628,12 +10048,12 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>OPERATING_DETERIORATION</t>
+          <t>WORKFORCE_REDUCTION</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>margin pressure</t>
+          <t>layoff；layoffs</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -9641,15 +10061,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>0673fc30b3e54fc5b8d29e382dbd059b</t>
+        </is>
+      </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>9557c75c7fa4f2cc72385ef6</t>
+          <t>321791372228eac0ca214be6</t>
         </is>
       </c>
       <c r="AD5" s="3" t="inlineStr">
         <is>
-          <t>b85fb47a39549e96690d81d4</t>
+          <t>14578c2488499cd965a7a8aa</t>
         </is>
       </c>
       <c r="AE5" s="3" t="inlineStr"/>
@@ -9662,7 +10086,11 @@
       <c r="AL5" s="3" t="inlineStr"/>
       <c r="AM5" s="3" t="inlineStr"/>
       <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="3" t="inlineStr"/>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr"/>
@@ -9681,7 +10109,7 @@
       <c r="BA5" s="3" t="inlineStr"/>
       <c r="BB5" s="3" t="inlineStr">
         <is>
-          <t>FISV</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="BC5" s="3" t="inlineStr">
@@ -9708,704 +10136,796 @@
       <c r="BH5" s="3" t="inlineStr"/>
       <c r="BI5" s="3" t="inlineStr"/>
       <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks Corporation</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Marathon Petroleum Corporation Common Stock</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Starbucks files another layoff notice for Seattle HQ, 200+ jobs affected</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Carson reaches $370-million settlement with Marathon Petroleum, resolving tax dispute</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>監管裁罰</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>0.745</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr"/>
+      <c r="S6" s="4" t="inlineStr"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcTNPaGlmWDVNendkZnp4UjZPTzdMQ2hONWh5SG5Dek9ZSXJqRzZaTjctLVYxRDd4QWdfZTM5LWZFT1F6N3pHU0lnN0tqeUF0TzBlNDA3ZlpEWGNiaDFqYlRBMEllOXE3RGZZU0pubkE2eHJGaldBNWtnT1JCenNQUk1kMWtUZm1vTlJvaGs1NkVaVmtERnM2MkdR?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>finance.yahoo.com</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr"/>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>37f6bc60fb4e4cd280132332527d361a</t>
+        </is>
+      </c>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>7544ac3ce7157c7987643cd1</t>
+        </is>
+      </c>
+      <c r="AD6" s="4" t="inlineStr">
+        <is>
+          <t>261167cb765c78558992776c</t>
+        </is>
+      </c>
+      <c r="AE6" s="4" t="inlineStr"/>
+      <c r="AF6" s="4" t="inlineStr"/>
+      <c r="AG6" s="4" t="inlineStr"/>
+      <c r="AH6" s="4" t="inlineStr"/>
+      <c r="AI6" s="4" t="inlineStr"/>
+      <c r="AJ6" s="4" t="inlineStr"/>
+      <c r="AK6" s="4" t="inlineStr"/>
+      <c r="AL6" s="4" t="inlineStr"/>
+      <c r="AM6" s="4" t="inlineStr"/>
+      <c r="AN6" s="4" t="inlineStr"/>
+      <c r="AO6" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>'-0.956</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiuAJBVV95cUxQWlRnaTdmazJ4N3IwcUtpSTFpZ2x0aEowUlhWWlBFRC1XVWxjWFktUUpXQmhxOTgweV9oSm02cUcxSmZGNmFlS1ltOWJoMHJvUjRfRUxhWGRXM2lCdTVYV1dTYTlFT1JsMWxGVUZfR0Z1VlNrMndzZnk4X2gzNTA1TXJVT2c4OHh4emZaZlhmbXZhbloyRV95U0pCbGxBQ0RER2tQUUxVOFdwdUExcDdLSlp6MEUzaWlxTjhhZzdUdEZ3R0YwUmJBenFVcTNVWm5rdDVRbFFyekFLYzV5aXM4VmpRLVprNnBROVB4cVZFUTVZelBFeXU0b3BsOU5VTlJXU0xDSkZGNHlIX0NyZm5pd1YxX21UMXhSRTR4bWp0ZE03LTVQdUZTbGU5aXgzM1NteTIyS3ZVcEE?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>KOMO</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>3de52fe7865a8ab9d3c5f24d</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>57fcfed4161a89c6cda80114</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>SBUX</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
+      <c r="AP6" s="4" t="inlineStr"/>
+      <c r="AQ6" s="4" t="inlineStr"/>
+      <c r="AR6" s="4" t="inlineStr"/>
+      <c r="AS6" s="4" t="inlineStr"/>
+      <c r="AT6" s="4" t="inlineStr"/>
+      <c r="AU6" s="4" t="inlineStr"/>
+      <c r="AV6" s="4" t="inlineStr"/>
+      <c r="AW6" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX6" s="4" t="inlineStr"/>
+      <c r="AY6" s="4" t="inlineStr"/>
+      <c r="AZ6" s="4" t="inlineStr"/>
+      <c r="BA6" s="4" t="inlineStr"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="BC6" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
+      <c r="BD6" s="4" t="inlineStr"/>
+      <c r="BE6" s="4" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.957209+00:00</t>
+        </is>
+      </c>
+      <c r="BG6" s="4" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
+      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Bunge Global</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Abbott Laboratories</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>How Revenue Growth Amid Margin Pressure Will Impact Bunge Global (BG) Investors</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Abbott in $670M settlement for some NEC infant formula claims (ABT:NYSE)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>'-0.492</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr"/>
+      <c r="S7" s="4" t="inlineStr"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNcWMxOVUxR0pMYkkwVmlQaGd3eUR0NnZkT2RoWnF2RzNVS1dVSlNHVVlQd1hfa05nN2p4MUFjRGdET2x2MTlvdW51cFpXVW1sWTRfNkRIZ0hVTjFtOHJuTnE2LVBBdWNHYWlLeXQ4b1dzUmlOWnRVcGRhOXV5cWkxbjdOcW00UVExWmVZQlA0dXc5NFpCU1E?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>eac60657ffd849dab62f5ba0a3ef54a4</t>
+        </is>
+      </c>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>1f0369a48bb25dc74096908b</t>
+        </is>
+      </c>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>202eba2fa538a72147f07e7f</t>
+        </is>
+      </c>
+      <c r="AE7" s="4" t="inlineStr"/>
+      <c r="AF7" s="4" t="inlineStr"/>
+      <c r="AG7" s="4" t="inlineStr"/>
+      <c r="AH7" s="4" t="inlineStr"/>
+      <c r="AI7" s="4" t="inlineStr"/>
+      <c r="AJ7" s="4" t="inlineStr"/>
+      <c r="AK7" s="4" t="inlineStr"/>
+      <c r="AL7" s="4" t="inlineStr"/>
+      <c r="AM7" s="4" t="inlineStr"/>
+      <c r="AN7" s="4" t="inlineStr"/>
+      <c r="AO7" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.239</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxOT1gyMkpjS3NWOExpbHVpV0pybzU1ZHp3d1JUVUd3M3JPWDh3YW03MmtnYWdQZjNJcDBCZVI2VzlZMzBCc3BqMmpFNWVDZllSYVNsNXp3a0FDaUw0ekh5YVNiSVI0R2lYa3dlQ0pKaUJ5SnRuZHBDbVBHa0JwbUwta2JlRFltd1l2VURzWFdFYTFzZWd4czBReE1oZ2dOc096eERkc1JncGJEejdTZGtScmNKRDJmdkt3dTUwLXpiTzM2ZnZQSG1DUU9oOTY1akZqSllJYno5c9IB3AFBVV95cUxQVUR3UFozVVRCQUJnRVI3M24tQmVPclJKQUZzdGM0OFNES2tKc0U2NmxjMHVjVkN2MVdXcVRoWjRGdVFUUHZVbW81dHN1RzdoSWlDMWFCNFNoNDRTX2swc0xEa1FBMEFrcVpJYUR5by02QnhzNkNuN1Bfd3JkSUhSTjh3NldtZkJUcFA2dktPZmQ1SXJBSGw4SEh2M203ajFPdDNMVUVTTW1vNWRXXzcxVFJIcUl0YU9kRFpYR2FmZEM2bWhIRWtVMWMwM25QT0pxenZyUUczSHN1TnN1?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>margin pressure</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>57d1f643bbd8d6fdb0f93bb9</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>ee61869adc7dc1e65e326d0e</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>BG</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
+      <c r="AP7" s="4" t="inlineStr"/>
+      <c r="AQ7" s="4" t="inlineStr"/>
+      <c r="AR7" s="4" t="inlineStr"/>
+      <c r="AS7" s="4" t="inlineStr"/>
+      <c r="AT7" s="4" t="inlineStr"/>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="AX7" s="4" t="inlineStr"/>
+      <c r="AY7" s="4" t="inlineStr"/>
+      <c r="AZ7" s="4" t="inlineStr"/>
+      <c r="BA7" s="4" t="inlineStr"/>
+      <c r="BB7" s="4" t="inlineStr">
+        <is>
+          <t>ABT</t>
+        </is>
+      </c>
+      <c r="BC7" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
+      <c r="BD7" s="4" t="inlineStr"/>
+      <c r="BE7" s="4" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
+        </is>
+      </c>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG7" s="4" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH7" s="4" t="inlineStr"/>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>Event_Code|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ7" s="4" t="inlineStr"/>
+      <c r="BK7" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>KeyCorp</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Warner Bros. Discovery</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>SB Nation Reacts Poll Results: Is Run Differential a Playoff Success Key</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>California Attorney General Rob Bonta: Paramount-WBD lawsuit is a 'black-and-white' antitrust case</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>'-0.552</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr"/>
+      <c r="Q8" s="4" t="inlineStr"/>
+      <c r="R8" s="4" t="inlineStr"/>
+      <c r="S8" s="4" t="inlineStr"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVGFJMndFT0FkV2Zfb1I3Qy1hQWFGV2tWVzJONzM2ODFLR0l3bjVhX3dCWVo4dnlMaERVYWhDVTB4dTlUNG1TMHJFSjZEcUgyR3kxSFhIb0tnWDVFRDVjeEcyTDBnV0ZWME5BMmxPbHl6NlR2Y2p0R1hkWDVtcDJ5dmJBcEJWMEpwQV9URi10WVVFMk5aYWR3bGJjNGhqZGhST2dwVWFGa3l0UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr"/>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>attorney general</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>962629bb4d8343d8b2df0a397aafd231</t>
+        </is>
+      </c>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>19ac0856711e24e1eb080c0e</t>
+        </is>
+      </c>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>00b3fe78af7ec9307af7c898</t>
+        </is>
+      </c>
+      <c r="AE8" s="4" t="inlineStr"/>
+      <c r="AF8" s="4" t="inlineStr"/>
+      <c r="AG8" s="4" t="inlineStr"/>
+      <c r="AH8" s="4" t="inlineStr"/>
+      <c r="AI8" s="4" t="inlineStr"/>
+      <c r="AJ8" s="4" t="inlineStr"/>
+      <c r="AK8" s="4" t="inlineStr"/>
+      <c r="AL8" s="4" t="inlineStr"/>
+      <c r="AM8" s="4" t="inlineStr"/>
+      <c r="AN8" s="4" t="inlineStr"/>
+      <c r="AO8" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUERxYXpCOHJWOHlpQW4yUDg5dkdSS3VHTzNSeDVDN0ltQjJDRlpOTFJ3dkdJa2pSV0JQSW1MX2llejY3Uy1DRVBqOW5xQ0hncFQySklZU2FFdTcyNklTLUdrTEpuS050U0tENW5JVHdBU2JtcVN6MWdKYXdGeDg1RTBTajFMdnY2Z1gtTEdoZUtRamtRZmo3bk9jTWFFbnVmdmxweHJvX3BmS25HU0VVb2M3MktqN1dWM0YwSThGYi1SLThhMTJ3UnhEYUJfUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>crawfishboxes.com</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>827e29b8562554996132c201</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>e15452dd3993cf8b4f47594b</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="3" t="inlineStr"/>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
+      <c r="AP8" s="4" t="inlineStr"/>
+      <c r="AQ8" s="4" t="inlineStr"/>
+      <c r="AR8" s="4" t="inlineStr"/>
+      <c r="AS8" s="4" t="inlineStr"/>
+      <c r="AT8" s="4" t="inlineStr"/>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
+      <c r="AX8" s="4" t="inlineStr"/>
+      <c r="AY8" s="4" t="inlineStr"/>
+      <c r="AZ8" s="4" t="inlineStr"/>
+      <c r="BA8" s="4" t="inlineStr"/>
+      <c r="BB8" s="4" t="inlineStr">
+        <is>
+          <t>WBD</t>
+        </is>
+      </c>
+      <c r="BC8" s="4" t="inlineStr">
+        <is>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD8" s="4" t="inlineStr"/>
+      <c r="BE8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF8" s="4" t="inlineStr"/>
+      <c r="BG8" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／交易所參照</t>
+        </is>
+      </c>
+      <c r="BH8" s="4" t="inlineStr"/>
+      <c r="BI8" s="4" t="inlineStr"/>
+      <c r="BJ8" s="4" t="inlineStr"/>
+      <c r="BK8" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>BBY</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Best Buy</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Pentair</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2026-08-20T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>Best Buy achieves zero waste goal at supply chain facilities</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>INVESTOR ALERT: Pomerantz Law Firm Reminds Investors with Losses on their Investment in Pentair plc of Class Action Lawsuit and Upcoming Deadlines - PNR</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>重大訴訟</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>'-0.881</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr"/>
+      <c r="Q9" s="4" t="inlineStr"/>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxPOUZMNDZmM1lPNFFKelBOQ3kyRDBQOENLY2JHNE5VbWhBbmN3N0Z1aGFmTVdrcjF2aTJaTDlZSS15cVk2ckNLeU1haGpnLUFPb2xCb2FLb2Z3b1cwMjdBZDZ5WmoxdVNYcGYtMWJjRTFyRFMwOGhsa1ozLVhfU2hoUXdxdVYzMXpqelNXelFqclpEeGlzUXJqbkpUUnhaOWNfempCWWZvRHM5LWpORW41U3FYMHNPSnZQX2REVlJyV29MakdhNEZUQVZla01aREpEZ2czbWxEblZoX3BGdDNLcnR2UHRZOUl0RU1WTUJrdTNPOE5yMXdqc0kxSUU4OTdhc0lmNW1YLVBmWG9pblpSM19sMUlZSi1MbGhzUENKMTZfdl9LcGN3S3dtNTE1NW8?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>prnewswire.com</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr"/>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>MAJOR_LITIGATION</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>class action</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>77c158a40ddc4258910ac1bc386e86a2</t>
+        </is>
+      </c>
+      <c r="AC9" s="4" t="inlineStr">
+        <is>
+          <t>5ddf20be53114d48c44012a2</t>
+        </is>
+      </c>
+      <c r="AD9" s="4" t="inlineStr">
+        <is>
+          <t>aa0e0d1cde37f85e1e33d68d</t>
+        </is>
+      </c>
+      <c r="AE9" s="4" t="inlineStr"/>
+      <c r="AF9" s="4" t="inlineStr"/>
+      <c r="AG9" s="4" t="inlineStr"/>
+      <c r="AH9" s="4" t="inlineStr"/>
+      <c r="AI9" s="4" t="inlineStr"/>
+      <c r="AJ9" s="4" t="inlineStr"/>
+      <c r="AK9" s="4" t="inlineStr"/>
+      <c r="AL9" s="4" t="inlineStr"/>
+      <c r="AM9" s="4" t="inlineStr"/>
+      <c r="AN9" s="4" t="inlineStr"/>
+      <c r="AO9" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0.665</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxQd3pOOHJGWjJZdXhzWXJxQjExdWYwU3dwR1RlbzEyWEgzT3JDUmNxWFIyMVNJa2tWaDYzdWxqZ1JHRnFRU1pERnR6Y05wdGlkUjM2NEpSekVHVmM2Sy1HYU9vMTV3NW9reUVxYi15eENsYVE1OVJJMWZLb2FPZlRORHo1RjB3eTFyWDJiWktHZ29peldLS29vdUt1clJjQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>esgdive.com</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="3" t="inlineStr">
-        <is>
-          <t>85d1addc8a08864dc793f988</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>9b91acd3984657a709b46053</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="inlineStr"/>
-      <c r="AF9" s="3" t="inlineStr"/>
-      <c r="AG9" s="3" t="inlineStr"/>
-      <c r="AH9" s="3" t="inlineStr"/>
-      <c r="AI9" s="3" t="inlineStr"/>
-      <c r="AJ9" s="3" t="inlineStr"/>
-      <c r="AK9" s="3" t="inlineStr"/>
-      <c r="AL9" s="3" t="inlineStr"/>
-      <c r="AM9" s="3" t="inlineStr"/>
-      <c r="AN9" s="3" t="inlineStr"/>
-      <c r="AO9" s="3" t="inlineStr"/>
-      <c r="AP9" s="3" t="inlineStr"/>
-      <c r="AQ9" s="3" t="inlineStr"/>
-      <c r="AR9" s="3" t="inlineStr"/>
-      <c r="AS9" s="3" t="inlineStr"/>
-      <c r="AT9" s="3" t="inlineStr"/>
-      <c r="AU9" s="3" t="inlineStr"/>
-      <c r="AV9" s="3" t="inlineStr"/>
-      <c r="AW9" s="3" t="inlineStr"/>
-      <c r="AX9" s="3" t="inlineStr"/>
-      <c r="AY9" s="3" t="inlineStr"/>
-      <c r="AZ9" s="3" t="inlineStr"/>
-      <c r="BA9" s="3" t="inlineStr"/>
-      <c r="BB9" s="3" t="inlineStr">
-        <is>
-          <t>BBY</t>
-        </is>
-      </c>
-      <c r="BC9" s="3" t="inlineStr">
+      <c r="AP9" s="4" t="inlineStr"/>
+      <c r="AQ9" s="4" t="inlineStr"/>
+      <c r="AR9" s="4" t="inlineStr"/>
+      <c r="AS9" s="4" t="inlineStr"/>
+      <c r="AT9" s="4" t="inlineStr"/>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr"/>
+      <c r="AX9" s="4" t="inlineStr"/>
+      <c r="AY9" s="4" t="inlineStr"/>
+      <c r="AZ9" s="4" t="inlineStr"/>
+      <c r="BA9" s="4" t="inlineStr"/>
+      <c r="BB9" s="4" t="inlineStr">
+        <is>
+          <t>PNR</t>
+        </is>
+      </c>
+      <c r="BC9" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD9" s="3" t="inlineStr"/>
-      <c r="BE9" s="3" t="inlineStr">
+      <c r="BD9" s="4" t="inlineStr"/>
+      <c r="BE9" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF9" s="3" t="inlineStr"/>
-      <c r="BG9" s="3" t="inlineStr">
+      <c r="BF9" s="4" t="inlineStr"/>
+      <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH9" s="3" t="inlineStr"/>
-      <c r="BI9" s="3" t="inlineStr"/>
-      <c r="BJ9" s="3" t="inlineStr"/>
-      <c r="BK9" s="3" t="inlineStr"/>
-      <c r="BL9" s="3" t="inlineStr"/>
+      <c r="BH9" s="4" t="inlineStr"/>
+      <c r="BI9" s="4" t="inlineStr"/>
+      <c r="BJ9" s="4" t="inlineStr"/>
+      <c r="BK9" s="4" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -10420,12 +10940,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Starbucks Corporation</t>
+          <t>PepsiCo, Inc.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -10435,7 +10955,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Starbucks layoffs hit 224 Seattle headquarters employees</t>
+          <t>Over 100 PepsiCo employees in Columbia facing permanent layoffs, documents show</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -10456,13 +10976,17 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -10472,7 +10996,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>'-0.959</t>
+          <t>'-0.962</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr"/>
@@ -10486,12 +11010,12 @@
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNLXBaMkcyQTUzUnFPa0I4OWduRXRBUnFNTml3TXhfV3BpbVh5Y082bVRFdkFSWG01aF9aWVJGWXRHMFBrNl9Hdk96eDFzYkxqRTVSVEdPQWY4SHVEcGY4TTNTWHA0NWxtdUlHeDRfY25oR0JVX3FvMDVGQnl1LUpEQUNKajRFUktOWGp3WE1XLVhEbmpfOUlsS2FENUd3d0pocldhZ05mOEZUcjJfUVHSAbMBQVVfeXFMTjlxSHpUbFdwd2ZhWXVQMGFTZ0xQMjNoQWVJeTgzWXE5aVh6cFFTTzY0eDB1eDRaRW9YZmtfb2lKRGVqZl90TTg0ak93MEI3ZGhPRzFGa09Bbk9xTnlScURocmJ5TnVxNFN0c0VzelNDaFdtZzZSYzVxcy01eW9pTlF0VDdDLUdCWDl0S0hiMThZQ2JkT09fMDloUHN0bnpzTGJWM0F6RVRtdkdDYzd2eVNNeFU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmJjaEc5ZW93MFFVY0tnUmVZQ0REMlJ2YkY5YkgyVm16d0kyRVVnNFZ3dW9UYmJ1aDQ4MXFvMHlfOURQVll6ajN4Nm90ejhQT3dHNWdqbmc1RTNqWEh6SU9PQjlsVDZjbWZzaXExRVR5Qzg2ZU5RTkZNbW9TWlJ4SjBsRUVwT3VUdlpiUWNobEtCMUJpNlo0NFQ0VENsZE5pZmNQX0JXeGVqOE9Qb0HSAcIBQVVfeXFMTjVVSDAxVnNlZUpSbEtwc3hOVWlLVW41QmlMaERyZkg2eDk3MHNNaWJlb2gzc19SOTByNG91aG05RTI0aHVNM3hteTk5VXM5YmkyUV8wZkpVOTdkS2JjaVdWR181Qndqc2NTa2swbWJJeXQ3RlZkeTVOYlBoUlhvRndvTVk0bkZBLWtUMWRHUlRrVDdfVklJSERjM090WVRyUjhwZEV5WncySHRNWV9BNGFmd3h0ZWo1OFdwMEdyOC0tYVE?oc=5</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t>FOX 13 Seattle</t>
+          <t>WIS News 10</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr"/>
@@ -10515,15 +11039,19 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>ee2b459ce4f145699a422057ec325b55</t>
+        </is>
+      </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>321791372228eac0ca214be6</t>
+          <t>197a030e866462b53c92be76</t>
         </is>
       </c>
       <c r="AD10" s="3" t="inlineStr">
         <is>
-          <t>14578c2488499cd965a7a8aa</t>
+          <t>094940ea9bbef65029c0ac7d</t>
         </is>
       </c>
       <c r="AE10" s="3" t="inlineStr"/>
@@ -10536,7 +11064,11 @@
       <c r="AL10" s="3" t="inlineStr"/>
       <c r="AM10" s="3" t="inlineStr"/>
       <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP10" s="3" t="inlineStr"/>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
@@ -10555,7 +11087,7 @@
       <c r="BA10" s="3" t="inlineStr"/>
       <c r="BB10" s="3" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="BC10" s="3" t="inlineStr">
@@ -10582,1147 +11114,19 @@
       <c r="BH10" s="3" t="inlineStr"/>
       <c r="BI10" s="3" t="inlineStr"/>
       <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>Marathon Petroleum Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Carson reaches $370-million settlement with Marathon Petroleum, resolving tax dispute</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>0.745</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxNcTNPaGlmWDVNendkZnp4UjZPTzdMQ2hONWh5SG5Dek9ZSXJqRzZaTjctLVYxRDd4QWdfZTM5LWZFT1F6N3pHU0lnN0tqeUF0TzBlNDA3ZlpEWGNiaDFqYlRBMEllOXE3RGZZU0pubkE2eHJGaldBNWtnT1JCenNQUk1kMWtUZm1vTlJvaGs1NkVaVmtERnM2MkdR?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>finance.yahoo.com</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="4" t="inlineStr">
-        <is>
-          <t>37f6bc60fb4e4cd280132332527d361a</t>
-        </is>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>7544ac3ce7157c7987643cd1</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>261167cb765c78558992776c</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>MPC</t>
-        </is>
-      </c>
-      <c r="BC11" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH11" s="4" t="inlineStr"/>
-      <c r="BI11" s="4" t="inlineStr"/>
-      <c r="BJ11" s="4" t="inlineStr"/>
-      <c r="BK11" s="4" t="inlineStr">
+      <c r="BK10" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL11" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>Abbott Laboratories</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Abbott in $670M settlement for some NEC infant formula claims (ABT:NYSE)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>'-0.492</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxNcWMxOVUxR0pMYkkwVmlQaGd3eUR0NnZkT2RoWnF2RzNVS1dVSlNHVVlQd1hfa05nN2p4MUFjRGdET2x2MTlvdW51cFpXVW1sWTRfNkRIZ0hVTjFtOHJuTnE2LVBBdWNHYWlLeXQ4b1dzUmlOWnRVcGRhOXV5cWkxbjdOcW00UVExWmVZQlA0dXc5NFpCU1E?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>eac60657ffd849dab62f5ba0a3ef54a4</t>
-        </is>
-      </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>1f0369a48bb25dc74096908b</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>202eba2fa538a72147f07e7f</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
-        <is>
-          <t>ABT</t>
-        </is>
-      </c>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
-        <is>
-          <t>https://www.sec.gov/Archives/edgar/data/1800/000162828026028357/R1.htm</t>
-        </is>
-      </c>
-      <c r="BF12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG12" s="4" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr">
-        <is>
-          <t>Event_Code|事件中文</t>
-        </is>
-      </c>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL12" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>Warner Bros. Discovery</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>California Attorney General Rob Bonta: Paramount-WBD lawsuit is a 'black-and-white' antitrust case</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>'-0.552</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr"/>
-      <c r="Q13" s="4" t="inlineStr"/>
-      <c r="R13" s="4" t="inlineStr"/>
-      <c r="S13" s="4" t="inlineStr"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVGFJMndFT0FkV2Zfb1I3Qy1hQWFGV2tWVzJONzM2ODFLR0l3bjVhX3dCWVo4dnlMaERVYWhDVTB4dTlUNG1TMHJFSjZEcUgyR3kxSFhIb0tnWDVFRDVjeEcyTDBnV0ZWME5BMmxPbHl6NlR2Y2p0R1hkWDVtcDJ5dmJBcEJWMEpwQV9URi10WVVFMk5aYWR3bGJjNGhqZGhST2dwVWFGa3l0UQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>CNBC</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr"/>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>attorney general</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>962629bb4d8343d8b2df0a397aafd231</t>
-        </is>
-      </c>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>19ac0856711e24e1eb080c0e</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>00b3fe78af7ec9307af7c898</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr"/>
-      <c r="AF13" s="4" t="inlineStr"/>
-      <c r="AG13" s="4" t="inlineStr"/>
-      <c r="AH13" s="4" t="inlineStr"/>
-      <c r="AI13" s="4" t="inlineStr"/>
-      <c r="AJ13" s="4" t="inlineStr"/>
-      <c r="AK13" s="4" t="inlineStr"/>
-      <c r="AL13" s="4" t="inlineStr"/>
-      <c r="AM13" s="4" t="inlineStr"/>
-      <c r="AN13" s="4" t="inlineStr"/>
-      <c r="AO13" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP13" s="4" t="inlineStr"/>
-      <c r="AQ13" s="4" t="inlineStr"/>
-      <c r="AR13" s="4" t="inlineStr"/>
-      <c r="AS13" s="4" t="inlineStr"/>
-      <c r="AT13" s="4" t="inlineStr"/>
-      <c r="AU13" s="4" t="inlineStr"/>
-      <c r="AV13" s="4" t="inlineStr"/>
-      <c r="AW13" s="4" t="inlineStr"/>
-      <c r="AX13" s="4" t="inlineStr"/>
-      <c r="AY13" s="4" t="inlineStr"/>
-      <c r="AZ13" s="4" t="inlineStr"/>
-      <c r="BA13" s="4" t="inlineStr"/>
-      <c r="BB13" s="4" t="inlineStr">
-        <is>
-          <t>WBD</t>
-        </is>
-      </c>
-      <c r="BC13" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD13" s="4" t="inlineStr"/>
-      <c r="BE13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF13" s="4" t="inlineStr"/>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH13" s="4" t="inlineStr"/>
-      <c r="BI13" s="4" t="inlineStr"/>
-      <c r="BJ13" s="4" t="inlineStr"/>
-      <c r="BK13" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL13" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>Pentair</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>INVESTOR ALERT: Pomerantz Law Firm Reminds Investors with Losses on their Investment in Pentair plc of Class Action Lawsuit and Upcoming Deadlines - PNR</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>'-0.881</t>
-        </is>
-      </c>
-      <c r="P14" s="4" t="inlineStr"/>
-      <c r="Q14" s="4" t="inlineStr"/>
-      <c r="R14" s="4" t="inlineStr"/>
-      <c r="S14" s="4" t="inlineStr"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirwJBVV95cUxPOUZMNDZmM1lPNFFKelBOQ3kyRDBQOENLY2JHNE5VbWhBbmN3N0Z1aGFmTVdrcjF2aTJaTDlZSS15cVk2ckNLeU1haGpnLUFPb2xCb2FLb2Z3b1cwMjdBZDZ5WmoxdVNYcGYtMWJjRTFyRFMwOGhsa1ozLVhfU2hoUXdxdVYzMXpqelNXelFqclpEeGlzUXJqbkpUUnhaOWNfempCWWZvRHM5LWpORW41U3FYMHNPSnZQX2REVlJyV29MakdhNEZUQVZla01aREpEZ2czbWxEblZoX3BGdDNLcnR2UHRZOUl0RU1WTUJrdTNPOE5yMXdqc0kxSUU4OTdhc0lmNW1YLVBmWG9pblpSM19sMUlZSi1MbGhzUENKMTZfdl9LcGN3S3dtNTE1NW8?oc=5</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>prnewswire.com</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr"/>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>77c158a40ddc4258910ac1bc386e86a2</t>
-        </is>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>5ddf20be53114d48c44012a2</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>aa0e0d1cde37f85e1e33d68d</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr"/>
-      <c r="AF14" s="4" t="inlineStr"/>
-      <c r="AG14" s="4" t="inlineStr"/>
-      <c r="AH14" s="4" t="inlineStr"/>
-      <c r="AI14" s="4" t="inlineStr"/>
-      <c r="AJ14" s="4" t="inlineStr"/>
-      <c r="AK14" s="4" t="inlineStr"/>
-      <c r="AL14" s="4" t="inlineStr"/>
-      <c r="AM14" s="4" t="inlineStr"/>
-      <c r="AN14" s="4" t="inlineStr"/>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="inlineStr"/>
-      <c r="AQ14" s="4" t="inlineStr"/>
-      <c r="AR14" s="4" t="inlineStr"/>
-      <c r="AS14" s="4" t="inlineStr"/>
-      <c r="AT14" s="4" t="inlineStr"/>
-      <c r="AU14" s="4" t="inlineStr"/>
-      <c r="AV14" s="4" t="inlineStr"/>
-      <c r="AW14" s="4" t="inlineStr"/>
-      <c r="AX14" s="4" t="inlineStr"/>
-      <c r="AY14" s="4" t="inlineStr"/>
-      <c r="AZ14" s="4" t="inlineStr"/>
-      <c r="BA14" s="4" t="inlineStr"/>
-      <c r="BB14" s="4" t="inlineStr">
-        <is>
-          <t>PNR</t>
-        </is>
-      </c>
-      <c r="BC14" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD14" s="4" t="inlineStr"/>
-      <c r="BE14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF14" s="4" t="inlineStr"/>
-      <c r="BG14" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH14" s="4" t="inlineStr"/>
-      <c r="BI14" s="4" t="inlineStr"/>
-      <c r="BJ14" s="4" t="inlineStr"/>
-      <c r="BK14" s="4" t="inlineStr">
-        <is>
-          <t>離線覆核</t>
-        </is>
-      </c>
-      <c r="BL14" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-26T15:42:35.885456+08:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>PepsiCo, Inc.</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>Over 100 PepsiCo employees in Columbia facing permanent layoffs, documents show</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>'-0.962</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPUmJjaEc5ZW93MFFVY0tnUmVZQ0REMlJ2YkY5YkgyVm16d0kyRVVnNFZ3dW9UYmJ1aDQ4MXFvMHlfOURQVll6ajN4Nm90ejhQT3dHNWdqbmc1RTNqWEh6SU9PQjlsVDZjbWZzaXExRVR5Qzg2ZU5RTkZNbW9TWlJ4SjBsRUVwT3VUdlpiUWNobEtCMUJpNlo0NFQ0VENsZE5pZmNQX0JXeGVqOE9Qb0HSAcIBQVVfeXFMTjVVSDAxVnNlZUpSbEtwc3hOVWlLVW41QmlMaERyZkg2eDk3MHNNaWJlb2gzc19SOTByNG91aG05RTI0aHVNM3hteTk5VXM5YmkyUV8wZkpVOTdkS2JjaVdWR181Qndqc2NTa2swbWJJeXQ3RlZkeTVOYlBoUlhvRndvTVk0bkZBLWtUMWRHUlRrVDdfVklJSERjM090WVRyUjhwZEV5WncySHRNWV9BNGFmd3h0ZWo1OFdwMEdyOC0tYVE?oc=5</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t>WIS News 10</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z15" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>197a030e866462b53c92be76</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>094940ea9bbef65029c0ac7d</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="inlineStr"/>
-      <c r="AF15" s="3" t="inlineStr"/>
-      <c r="AG15" s="3" t="inlineStr"/>
-      <c r="AH15" s="3" t="inlineStr"/>
-      <c r="AI15" s="3" t="inlineStr"/>
-      <c r="AJ15" s="3" t="inlineStr"/>
-      <c r="AK15" s="3" t="inlineStr"/>
-      <c r="AL15" s="3" t="inlineStr"/>
-      <c r="AM15" s="3" t="inlineStr"/>
-      <c r="AN15" s="3" t="inlineStr"/>
-      <c r="AO15" s="3" t="inlineStr"/>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
-      <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
-      <c r="AU15" s="3" t="inlineStr"/>
-      <c r="AV15" s="3" t="inlineStr"/>
-      <c r="AW15" s="3" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX15" s="3" t="inlineStr"/>
-      <c r="AY15" s="3" t="inlineStr"/>
-      <c r="AZ15" s="3" t="inlineStr"/>
-      <c r="BA15" s="3" t="inlineStr"/>
-      <c r="BB15" s="3" t="inlineStr">
-        <is>
-          <t>PEP</t>
-        </is>
-      </c>
-      <c r="BC15" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD15" s="3" t="inlineStr"/>
-      <c r="BE15" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF15" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG15" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH15" s="3" t="inlineStr"/>
-      <c r="BI15" s="3" t="inlineStr"/>
-      <c r="BJ15" s="3" t="inlineStr"/>
-      <c r="BK15" s="3" t="inlineStr"/>
-      <c r="BL15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>International Business Machines Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20T04:01:00+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>IBM’s 2026 Data Breach Report: Houston, We Have A Problem</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>'-0.946</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNUXZUWlJkaXVxNldYVjRSMXowQ0xFTWw2SXcwdVppbUFsR05qWVFIejc3eXNoMkRSWnVxaVdtS0RjcC1DVVZtN0FxLTJMNHlzMEdpS3IxSUhUMW5DcmMxbW5SUkl6VF8wZnFaM2Ytd1gzR3AzNE1CR3J3djQxNlE5Y2M0X0N0Z0xJN21ZTEtYYXU?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="3" t="inlineStr">
-        <is>
-          <t>Above the Law</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr">
-        <is>
-          <t>2ff2c3663d180b21905740d5</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>b5fb7ce9cc34eee18630b78a</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="inlineStr"/>
-      <c r="AF16" s="3" t="inlineStr"/>
-      <c r="AG16" s="3" t="inlineStr"/>
-      <c r="AH16" s="3" t="inlineStr"/>
-      <c r="AI16" s="3" t="inlineStr"/>
-      <c r="AJ16" s="3" t="inlineStr"/>
-      <c r="AK16" s="3" t="inlineStr"/>
-      <c r="AL16" s="3" t="inlineStr"/>
-      <c r="AM16" s="3" t="inlineStr"/>
-      <c r="AN16" s="3" t="inlineStr"/>
-      <c r="AO16" s="3" t="inlineStr"/>
-      <c r="AP16" s="3" t="inlineStr"/>
-      <c r="AQ16" s="3" t="inlineStr"/>
-      <c r="AR16" s="3" t="inlineStr"/>
-      <c r="AS16" s="3" t="inlineStr"/>
-      <c r="AT16" s="3" t="inlineStr"/>
-      <c r="AU16" s="3" t="inlineStr"/>
-      <c r="AV16" s="3" t="inlineStr"/>
-      <c r="AW16" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX16" s="3" t="inlineStr"/>
-      <c r="AY16" s="3" t="inlineStr"/>
-      <c r="AZ16" s="3" t="inlineStr"/>
-      <c r="BA16" s="3" t="inlineStr"/>
-      <c r="BB16" s="3" t="inlineStr">
-        <is>
-          <t>IBM</t>
-        </is>
-      </c>
-      <c r="BC16" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD16" s="3" t="inlineStr"/>
-      <c r="BE16" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF16" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG16" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH16" s="3" t="inlineStr"/>
-      <c r="BI16" s="3" t="inlineStr"/>
-      <c r="BJ16" s="3" t="inlineStr"/>
-      <c r="BK16" s="3" t="inlineStr"/>
-      <c r="BL16" s="3" t="inlineStr"/>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL16"/>
+  <autoFilter ref="A1:BL10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11733,7 +11137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL9"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12124,1400 +11528,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Caterpillar Inc.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T23:12:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>More than 700 cats survive Hurricane Lala as Hawaii cat sanctuary faces $20K in damage</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>'-0.233</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxPak8yNzBSVXB6am9kdnZhRms0Unc2eVBHNkw3T3pfbU1EY3RSeU8tMHFwMEdwaDhfNk1yQ21LdFVEeUNnYjk3Z2lWVXdtUWZhRkJIWXhuYnFqU25UREx0TUM4VmlGZ2FVV2R6QWtyUWVLMjdNZW82b3NNZTJGTUFmbHJ3dGxzeGhiRWdudHRjZ19fLWtob2dZZkZTeU9VMi16YTdIaUtKb09uWkNFeFlDaW1ORlowRkVWUGVtUk9qTGlNWEJHS2lYQzhrZGtpcFM1OXdNdkVWbnR2S3NIaTRlWUpMMEFlcTlmVlZkTmhlVk5qMlZ0?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>newscentermaine.com</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>13b919f6499b102da762eade</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>fb3022116b0e83adc2eeb886</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T23:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>One month of wildfires has cost Washington state over $200 million</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>'-0.924</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxONmlRS1ZzVlFLeDNqTElqR0RXRHNGV1BiZThCdTVCVlFQc3NzeHpWa3NUUkFhMzA0eHR3VVFET3hyWjlXdkVEODFieXFFZldFeEt4eHY2WVlEb2tHaVNxdnljU2I1TFpkOERocXhXVTJwb3lYb3JYeFRNNjVQTXpSaDdTci1KTVVGc0w0M2JKVU9nbGNWZXVod3FSZXFhY2IyQmVZOEpnQUpiZkV6MUE?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Planetizen</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>6b6667dfea00d2582f92d3ba</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>c6d550ce7518a6317ddb4658</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr"/>
-      <c r="BF3" s="2" t="inlineStr"/>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Citigroup</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T20:18:30+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Nevada Air Guard C-130 departs Reno to support western wildfire fight</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>'-0.032</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOUWNJTjdVYk5UYjI1QU1NZnoxVW5QTVZqNjFkQVlKTENnVkFELWREUTRQV3pNU3V2cm9aN1BhRS1PZ2RLUVZBV01vMGNGUEc4NkhMXzJURUJoNjFubkFZa2ZUM2RiMkVFME9hYlBudW9mWGhCLXd0M2hBWHdzQVIyUHZFRl91R21tZ1I2SV9ab1dVMDFhYWtGR3ZXWHdzSC1lbEdxZUJmdFFVRWJFRzhjWk13eEJqZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>dailydispatch.com</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>5856b4783cb46f4b6d26b806</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>c07fb26c29fb7542aebd1033</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr"/>
-      <c r="AI4" s="2" t="inlineStr"/>
-      <c r="AJ4" s="2" t="inlineStr"/>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr"/>
-      <c r="AQ4" s="2" t="inlineStr"/>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr"/>
-      <c r="AT4" s="2" t="inlineStr"/>
-      <c r="AU4" s="2" t="inlineStr"/>
-      <c r="AV4" s="2" t="inlineStr"/>
-      <c r="AW4" s="2" t="inlineStr"/>
-      <c r="AX4" s="2" t="inlineStr"/>
-      <c r="AY4" s="2" t="inlineStr"/>
-      <c r="AZ4" s="2" t="inlineStr"/>
-      <c r="BA4" s="2" t="inlineStr"/>
-      <c r="BB4" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BC4" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BE4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="2" t="inlineStr"/>
-      <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
-      <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>KeyCorp</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>SB Nation Reacts Poll Results: Is Run Differential a Playoff Success Key</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOUERxYXpCOHJWOHlpQW4yUDg5dkdSS3VHTzNSeDVDN0ltQjJDRlpOTFJ3dkdJa2pSV0JQSW1MX2llejY3Uy1DRVBqOW5xQ0hncFQySklZU2FFdTcyNklTLUdrTEpuS050U0tENW5JVHdBU2JtcVN6MWdKYXdGeDg1RTBTajFMdnY2Z1gtTEdoZUtRamtRZmo3bk9jTWFFbnVmdmxweHJvX3BmS25HU0VVb2M3MktqN1dWM0YwSThGYi1SLThhMTJ3UnhEYUJfUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t>crawfishboxes.com</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="3" t="inlineStr">
-        <is>
-          <t>827e29b8562554996132c201</t>
-        </is>
-      </c>
-      <c r="AD5" s="3" t="inlineStr">
-        <is>
-          <t>e15452dd3993cf8b4f47594b</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="inlineStr"/>
-      <c r="AF5" s="3" t="inlineStr"/>
-      <c r="AG5" s="3" t="inlineStr"/>
-      <c r="AH5" s="3" t="inlineStr"/>
-      <c r="AI5" s="3" t="inlineStr"/>
-      <c r="AJ5" s="3" t="inlineStr"/>
-      <c r="AK5" s="3" t="inlineStr"/>
-      <c r="AL5" s="3" t="inlineStr"/>
-      <c r="AM5" s="3" t="inlineStr"/>
-      <c r="AN5" s="3" t="inlineStr"/>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr"/>
-      <c r="AQ5" s="3" t="inlineStr"/>
-      <c r="AR5" s="3" t="inlineStr"/>
-      <c r="AS5" s="3" t="inlineStr"/>
-      <c r="AT5" s="3" t="inlineStr"/>
-      <c r="AU5" s="3" t="inlineStr"/>
-      <c r="AV5" s="3" t="inlineStr"/>
-      <c r="AW5" s="3" t="inlineStr"/>
-      <c r="AX5" s="3" t="inlineStr"/>
-      <c r="AY5" s="3" t="inlineStr"/>
-      <c r="AZ5" s="3" t="inlineStr"/>
-      <c r="BA5" s="3" t="inlineStr"/>
-      <c r="BB5" s="3" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BC5" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="3" t="inlineStr">
-        <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="BE5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="3" t="inlineStr"/>
-      <c r="BH5" s="3" t="inlineStr"/>
-      <c r="BI5" s="3" t="inlineStr"/>
-      <c r="BJ5" s="3" t="inlineStr"/>
-      <c r="BK5" s="3" t="inlineStr"/>
-      <c r="BL5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Fastenal</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Fast-spreading wildfire threatens structures near China Spring</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>'-0.909</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi2wFBVV95cUxOUS15ckRkc1VKWWstYjdFOWZnbmlTWE9pQWNhZ0swM3hzN1VDSzJpX01tQU9wT1QybVVWc2tSbTRuQjN6Qm1DT0NIUlFJQWc0SElvVWZXdHY1djNTYWZEU3Bxa0U4WDNOMFpjN2NuQ0IzT1pUZzNkVGJMd0V2TmV0TVlOaWVaQ1ZwQldwLWJ5dFlOR0taTl93LVBWZFVSV0pTRUczUmhxd3BWaFFkSjlEWFItOXJJWGl0MWVLdXpMYXd1VFVZeHVLN2FHOExfSnlIQzM1RDJWWWs1LXM?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>KCENTV.com</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr"/>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>710d96aeafcd9dd89a0947b6</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>d1b990d8b8cd706ccea45a4c</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BE6" s="2" t="inlineStr"/>
-      <c r="BF6" s="2" t="inlineStr"/>
-      <c r="BG6" s="2" t="inlineStr"/>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Fastenal</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>WATCH: New video shows fast-moving water flood Metro bus during July storms</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0.037</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxQRWxxRV9TdUtBbzFKaWNmLVV1TmRINlRVNmFhUVNTNFp3bzRnektMNndwcERXV2JuYTQ2dUltN05paWJBaWJJS0pEampBLWk5cnJEVXpxcjk3RDRqVVV0NU94M3JEQkFSdjR5Q0pNSlM1cHkzeWNyR3kxd1llcXB2b3htdEtndjNud0Focg?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>WLWT</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr"/>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>ba8d55b8d4bcb962a9c92d34</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>db070a980a254deb9b99b516</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr"/>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BC7" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD7" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BE7" s="2" t="inlineStr"/>
-      <c r="BF7" s="2" t="inlineStr"/>
-      <c r="BG7" s="2" t="inlineStr"/>
-      <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
-      <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>O’Reilly Automotive</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Former Marines Orly Guteza reportedly detailed in his recantation how his former statements had been forced upon him so he could link Leyte 1st District Rep. Martin Romualdez to the flood control controversy. https://tinyurl.com/5cyhaehr</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>'-0.233</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxPU0JWZ1Vfd01oa0VCTGtRVlFuTnZRMHJDNnZPblJoYmF2U2htQU1HSEFYOGs2ZjlxWUJKemR4X2pxNXRfbWFZdTFWZXZKZ0VrSEdXRGtDN1V6TmZESjNwdnFnLWFwY3piOGJRSGNxSVJYaE1VNFB2Nm1JV2U4eW5nN3ZhVWdpZVVrUjRJck5SX1E2VDZ3TW9nZEZwLVYxMEduOEpOLXl3UXh1eks3V2lINWNveENDQnRvb0E3R0dkVW5yTkhjRjd1X2VHd2dpd0hxRWV3ZEJBbWt1VlJE?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>facebook.com</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr"/>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>815071602ea7a305ed23b696</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>b52b9dfcd55a0b7eb55b1761</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr"/>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>ORLY</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr">
-        <is>
-          <t>ORLY</t>
-        </is>
-      </c>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="2" t="inlineStr"/>
-      <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
-      <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Fastenal</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-20T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Fast-moving wildfires leave forests less able to recover, Western study finds</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>'-0.849</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNSHVNc042bjFPcmNacmpBRDhJZUVMaEk2clhXSnk5U1pvWTMwN0pqN1hxbkdsMEhHc09LMEdVRlhwMkdmUDlOTXZZYUU3SzlfSTRsVTBkcGtOaVI0R1cyNVo0ZXFLV0NuSWR5U2lJNndfWjJfYjloVGtNNU5KdTRsWFRJd2RaUUVwUzFmb0xhdkU4Y1NhbXdSd2ZxTmJuY2hMWC1Ub2k5U3ZwYlpvdlVWLXFWeHR6QjRKMXFYSg?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Gunnison Country Times</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr"/>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>wildfire</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>f36621694d50360b5a1091ee</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>67c3e7e284a83a649e23c686</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr"/>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="2" t="inlineStr">
-        <is>
-          <t>FAST</t>
-        </is>
-      </c>
-      <c r="BE9" s="2" t="inlineStr"/>
-      <c r="BF9" s="2" t="inlineStr"/>
-      <c r="BG9" s="2" t="inlineStr"/>
-      <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
-      <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL9"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-20.xlsx
+++ b/news_daily/2026-08-20.xlsx
@@ -888,28 +888,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -962,7 +966,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>d86e1723f5a74b28a236dac06f2c232f</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>708278669bc1302f23c9d73d</t>
@@ -983,7 +991,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1027,10 +1039,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1446,28 +1470,32 @@
       <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1507,7 +1535,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1520,7 +1548,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>a2a57d8706274861b28fdd91ca8df0b1</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>c633afed2bd6935d6acf35ed</t>
@@ -1541,7 +1573,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1585,10 +1621,22 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1818,28 +1866,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1879,7 +1931,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1892,7 +1944,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>9aaf37f4ac9b40c18f6e86994428159f</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>b8a5f0196f4b9516908e7edd</t>
@@ -1913,7 +1969,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1957,10 +2017,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -4356,28 +4428,32 @@
       <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4417,7 +4493,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -4430,7 +4506,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>bc6c2dfba4ff416f80a2e0c0c73668cd</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>2ccc0c19ff00898fa70652d9</t>
@@ -4451,7 +4531,11 @@
       <c r="AL20" s="2" t="inlineStr"/>
       <c r="AM20" s="2" t="inlineStr"/>
       <c r="AN20" s="2" t="inlineStr"/>
-      <c r="AO20" s="2" t="inlineStr"/>
+      <c r="AO20" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP20" s="2" t="inlineStr"/>
       <c r="AQ20" s="2" t="inlineStr"/>
       <c r="AR20" s="2" t="inlineStr"/>
@@ -4495,10 +4579,22 @@
         </is>
       </c>
       <c r="BH20" s="2" t="inlineStr"/>
-      <c r="BI20" s="2" t="inlineStr"/>
+      <c r="BI20" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ20" s="2" t="inlineStr"/>
-      <c r="BK20" s="2" t="inlineStr"/>
-      <c r="BL20" s="2" t="inlineStr"/>
+      <c r="BK20" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -5912,28 +6008,32 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5973,7 +6073,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -5986,7 +6086,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>2293039addb044d3b4aae2db4e70c0a8</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>5db727afab008aee6f41a79c</t>
@@ -6007,7 +6111,11 @@
       <c r="AL28" s="2" t="inlineStr"/>
       <c r="AM28" s="2" t="inlineStr"/>
       <c r="AN28" s="2" t="inlineStr"/>
-      <c r="AO28" s="2" t="inlineStr"/>
+      <c r="AO28" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP28" s="2" t="inlineStr"/>
       <c r="AQ28" s="2" t="inlineStr"/>
       <c r="AR28" s="2" t="inlineStr"/>
@@ -6043,10 +6151,22 @@
         </is>
       </c>
       <c r="BH28" s="2" t="inlineStr"/>
-      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6082,28 +6202,32 @@
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6143,7 +6267,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -6156,7 +6280,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>29ac3003a9d0465f96f0911047123dd9</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>b2794f97eab15a7f3707de6d</t>
@@ -6177,7 +6305,11 @@
       <c r="AL29" s="2" t="inlineStr"/>
       <c r="AM29" s="2" t="inlineStr"/>
       <c r="AN29" s="2" t="inlineStr"/>
-      <c r="AO29" s="2" t="inlineStr"/>
+      <c r="AO29" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP29" s="2" t="inlineStr"/>
       <c r="AQ29" s="2" t="inlineStr"/>
       <c r="AR29" s="2" t="inlineStr"/>
@@ -6221,10 +6353,22 @@
         </is>
       </c>
       <c r="BH29" s="2" t="inlineStr"/>
-      <c r="BI29" s="2" t="inlineStr"/>
+      <c r="BI29" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ29" s="2" t="inlineStr"/>
-      <c r="BK29" s="2" t="inlineStr"/>
-      <c r="BL29" s="2" t="inlineStr"/>
+      <c r="BK29" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6632,28 +6776,32 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -6693,7 +6841,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -6706,7 +6854,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>399e04b65b6b4798bfb31019dde05044</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
           <t>b2b550dde47d47227cfc1141</t>
@@ -6727,7 +6879,11 @@
       <c r="AL32" s="2" t="inlineStr"/>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
-      <c r="AO32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP32" s="2" t="inlineStr"/>
       <c r="AQ32" s="2" t="inlineStr"/>
       <c r="AR32" s="2" t="inlineStr"/>
@@ -6771,10 +6927,22 @@
         </is>
       </c>
       <c r="BH32" s="2" t="inlineStr"/>
-      <c r="BI32" s="2" t="inlineStr"/>
+      <c r="BI32" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ32" s="2" t="inlineStr"/>
-      <c r="BK32" s="2" t="inlineStr"/>
-      <c r="BL32" s="2" t="inlineStr"/>
+      <c r="BK32" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6810,28 +6978,32 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6871,7 +7043,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -6884,7 +7056,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>ca0fc1f343224bf790c8ffe6a489852d</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>f6a794d3cbfdb48b9743955b</t>
@@ -6905,7 +7081,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6949,10 +7129,22 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
-      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ33" s="2" t="inlineStr"/>
-      <c r="BK33" s="2" t="inlineStr"/>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -7182,28 +7374,32 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7243,7 +7439,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -7256,7 +7452,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>5ac5ac538e744c57a6c637247a370d9c</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>bece0621b2f66193bac5083f</t>
@@ -7277,7 +7477,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -7321,10 +7525,22 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
-      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7684,28 +7900,32 @@
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -7745,7 +7965,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -7758,7 +7978,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>45b74916f6f9408d9b216d4a4f1db5a0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
           <t>5bbd4009dab83c51a3099be0</t>
@@ -7779,7 +8003,11 @@
       <c r="AL38" s="2" t="inlineStr"/>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
-      <c r="AO38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP38" s="2" t="inlineStr"/>
       <c r="AQ38" s="2" t="inlineStr"/>
       <c r="AR38" s="2" t="inlineStr"/>
@@ -7823,10 +8051,22 @@
         </is>
       </c>
       <c r="BH38" s="2" t="inlineStr"/>
-      <c r="BI38" s="2" t="inlineStr"/>
+      <c r="BI38" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ38" s="2" t="inlineStr"/>
-      <c r="BK38" s="2" t="inlineStr"/>
-      <c r="BL38" s="2" t="inlineStr"/>
+      <c r="BK38" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7862,28 +8102,32 @@
       <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -7923,7 +8167,7 @@
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -7936,7 +8180,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>84c1e35a51e54004b5eb4c511be1dd60</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
           <t>3983a527a408b90e06afc900</t>
@@ -7957,7 +8205,11 @@
       <c r="AL39" s="2" t="inlineStr"/>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
-      <c r="AO39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP39" s="2" t="inlineStr"/>
       <c r="AQ39" s="2" t="inlineStr"/>
       <c r="AR39" s="2" t="inlineStr"/>
@@ -8001,10 +8253,22 @@
         </is>
       </c>
       <c r="BH39" s="2" t="inlineStr"/>
-      <c r="BI39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ39" s="2" t="inlineStr"/>
-      <c r="BK39" s="2" t="inlineStr"/>
-      <c r="BL39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -8040,28 +8304,32 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -8101,7 +8369,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -8114,7 +8382,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>00d717a8a725421994289b0074af3064</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>a3776da920d52b29abb77e34</t>
@@ -8135,7 +8407,11 @@
       <c r="AL40" s="2" t="inlineStr"/>
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr"/>
-      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP40" s="2" t="inlineStr"/>
       <c r="AQ40" s="2" t="inlineStr"/>
       <c r="AR40" s="2" t="inlineStr"/>
@@ -8171,10 +8447,22 @@
         </is>
       </c>
       <c r="BH40" s="2" t="inlineStr"/>
-      <c r="BI40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ40" s="2" t="inlineStr"/>
-      <c r="BK40" s="2" t="inlineStr"/>
-      <c r="BL40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">

--- a/news_daily/2026-08-20.xlsx
+++ b/news_daily/2026-08-20.xlsx
@@ -7576,17 +7576,17 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -7594,7 +7594,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -7637,7 +7641,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -7650,7 +7654,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>b1ba704575404172a26584497c961850</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>801d89c94d0ec293eaff130b</t>
@@ -7671,7 +7679,11 @@
       <c r="AL36" s="2" t="inlineStr"/>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
-      <c r="AO36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP36" s="2" t="inlineStr"/>
       <c r="AQ36" s="2" t="inlineStr"/>
       <c r="AR36" s="2" t="inlineStr"/>
@@ -7699,10 +7711,22 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
-      <c r="BI36" s="2" t="inlineStr"/>
+      <c r="BI36" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ36" s="2" t="inlineStr"/>
-      <c r="BK36" s="2" t="inlineStr"/>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7738,17 +7762,17 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -7756,7 +7780,11 @@
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
           <t>True</t>
@@ -7799,7 +7827,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7812,7 +7840,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>16cc6ecd1aa44353a51290c2969eb93e</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>801d89c94d0ec293eaff130b</t>
@@ -7833,7 +7865,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7861,10 +7897,22 @@
           <t>保留人工代號；目前新聞文字無法自動佐證</t>
         </is>
       </c>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:26:33.476936+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
